--- a/Sistemas_Operativos/Ej12-TP2.xlsx
+++ b/Sistemas_Operativos/Ej12-TP2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\Facultad\2026\Primer-Cuatrimestre\Sistemas_Operativos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fernando\Desktop\Facultad\2026\Primer-Cuatrimestre\Sistemas_Operativos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80FF8CA-DCBE-4C6A-9ED0-A1499C09A43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C895E69-4CFF-404F-A46D-1FB472C2CDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="12948" windowHeight="12336" xr2:uid="{74129C9D-D7F7-4DCE-9C10-9263450FA96D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{74129C9D-D7F7-4DCE-9C10-9263450FA96D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="21">
   <si>
     <t>P1</t>
   </si>
@@ -73,12 +73,42 @@
   <si>
     <t>E/S</t>
   </si>
+  <si>
+    <t>Algoritmo SFJ con desalojo</t>
+  </si>
+  <si>
+    <t>I/O</t>
+  </si>
+  <si>
+    <t>Prioridad con desalojo y sin desalojo</t>
+  </si>
+  <si>
+    <t>RR con quantum de 5 unidades de tiempo</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>TE</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,16 +122,65 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF47878"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="20">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -380,11 +459,61 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -399,6 +528,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -408,15 +572,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -426,42 +581,203 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFF47878"/>
+      <color rgb="FFCC3300"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -790,174 +1106,472 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC130D8-FCBC-4B88-9E08-2961DB4326D5}">
-  <dimension ref="B1:BK19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:BP85"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.44140625" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
-    <col min="3" max="11" width="3.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="63" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="12" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="63" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="3.42578125" customWidth="1"/>
+    <col min="65" max="65" width="4.5703125" customWidth="1"/>
+    <col min="66" max="66" width="4.42578125" customWidth="1"/>
+    <col min="67" max="68" width="4.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:63" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="2:63" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="8"/>
-      <c r="W3" t="s">
+      <c r="T3" s="20"/>
+      <c r="U3" s="20"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="X3" s="25"/>
+      <c r="Y3" s="25"/>
+      <c r="Z3" s="25"/>
+      <c r="AA3" s="25"/>
+      <c r="AB3" s="25"/>
+      <c r="AC3" s="25"/>
+      <c r="AD3" s="25"/>
+      <c r="AE3" s="25"/>
+      <c r="AF3" s="25"/>
+      <c r="AG3" s="25"/>
+      <c r="AH3" s="25"/>
+      <c r="AI3" s="25"/>
+      <c r="AJ3" s="25"/>
+      <c r="AK3" s="25"/>
+      <c r="AL3" s="25"/>
+      <c r="AM3" s="25"/>
+      <c r="AN3" s="25"/>
+      <c r="AO3" s="25"/>
+      <c r="AP3" s="25"/>
+      <c r="AQ3" s="25"/>
+      <c r="AR3" s="25"/>
+      <c r="AS3" s="25"/>
+      <c r="AT3" s="25"/>
+      <c r="AU3" s="25"/>
+      <c r="AV3" s="25"/>
+      <c r="AW3" s="25"/>
+      <c r="AX3" s="25"/>
+      <c r="AY3" s="25"/>
+      <c r="AZ3" s="25"/>
+      <c r="BA3" s="25"/>
+      <c r="BB3" s="25"/>
+      <c r="BC3" s="25"/>
+      <c r="BD3" s="25"/>
+      <c r="BE3" s="25"/>
+      <c r="BF3" s="25"/>
+      <c r="BG3" s="25"/>
+      <c r="BH3" s="25"/>
+      <c r="BI3" s="25"/>
+      <c r="BJ3" s="25"/>
+      <c r="BK3" s="26"/>
     </row>
-    <row r="4" spans="2:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="W4" s="22"/>
-      <c r="X4" s="22"/>
-      <c r="Y4" s="22"/>
-      <c r="Z4" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="8"/>
-      <c r="AB4" t="s">
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="21"/>
+      <c r="AB4" s="27" t="s">
         <v>10</v>
       </c>
+      <c r="AC4" s="27"/>
+      <c r="AD4" s="27"/>
+      <c r="AE4" s="27"/>
       <c r="AF4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AG4" s="27" t="s">
         <v>9</v>
       </c>
+      <c r="AH4" s="27"/>
+      <c r="AI4" s="27"/>
+      <c r="AJ4" s="27"/>
+      <c r="AK4" s="27"/>
+      <c r="AL4" s="27"/>
+      <c r="AM4" s="27"/>
+      <c r="AN4" s="27"/>
+      <c r="AO4" s="27"/>
+      <c r="AP4" s="27"/>
+      <c r="AQ4" s="27"/>
+      <c r="AR4" s="27"/>
+      <c r="AS4" s="27"/>
+      <c r="AT4" s="27"/>
+      <c r="AU4" s="27"/>
+      <c r="AV4" s="27"/>
+      <c r="AW4" s="27"/>
+      <c r="AX4" s="27"/>
+      <c r="AY4" s="27"/>
+      <c r="AZ4" s="27"/>
+      <c r="BA4" s="27"/>
+      <c r="BB4" s="27"/>
+      <c r="BC4" s="27"/>
+      <c r="BD4" s="27"/>
+      <c r="BE4" s="27"/>
+      <c r="BF4" s="27"/>
+      <c r="BG4" s="27"/>
+      <c r="BH4" s="27"/>
+      <c r="BI4" s="27"/>
+      <c r="BJ4" s="27"/>
+      <c r="BK4" s="28"/>
     </row>
-    <row r="5" spans="2:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="W5" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="8"/>
-      <c r="Z5" s="22" t="s">
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+      <c r="W5" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="21"/>
+      <c r="Z5" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="AA5" s="22"/>
-      <c r="AD5" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE5" s="8"/>
-      <c r="AF5" t="s">
+      <c r="AA5" s="27"/>
+      <c r="AB5" s="27"/>
+      <c r="AC5" s="27"/>
+      <c r="AD5" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE5" s="21"/>
+      <c r="AF5" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="AL5" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="AM5" s="7"/>
-      <c r="AN5" s="7"/>
-      <c r="AO5" s="8"/>
-      <c r="AP5" t="s">
+      <c r="AG5" s="27"/>
+      <c r="AH5" s="27"/>
+      <c r="AI5" s="27"/>
+      <c r="AJ5" s="27"/>
+      <c r="AK5" s="27"/>
+      <c r="AL5" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM5" s="20"/>
+      <c r="AN5" s="20"/>
+      <c r="AO5" s="21"/>
+      <c r="AP5" s="27" t="s">
         <v>9</v>
       </c>
+      <c r="AQ5" s="27"/>
+      <c r="AR5" s="27"/>
+      <c r="AS5" s="27"/>
+      <c r="AT5" s="27"/>
+      <c r="AU5" s="27"/>
+      <c r="AV5" s="27"/>
+      <c r="AW5" s="27"/>
+      <c r="AX5" s="27"/>
+      <c r="AY5" s="27"/>
+      <c r="AZ5" s="27"/>
+      <c r="BA5" s="27"/>
+      <c r="BB5" s="27"/>
+      <c r="BC5" s="27"/>
+      <c r="BD5" s="27"/>
+      <c r="BE5" s="27"/>
+      <c r="BF5" s="27"/>
+      <c r="BG5" s="27"/>
+      <c r="BH5" s="27"/>
+      <c r="BI5" s="27"/>
+      <c r="BJ5" s="27"/>
+      <c r="BK5" s="28"/>
     </row>
-    <row r="6" spans="2:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="8"/>
-      <c r="S6" t="s">
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="21"/>
+      <c r="S6" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="AB6" s="22"/>
-      <c r="AC6" s="22"/>
-      <c r="AD6" s="22"/>
-      <c r="AE6" s="22"/>
-      <c r="AF6" s="22"/>
-      <c r="AG6" s="22"/>
-      <c r="AH6" s="22"/>
-      <c r="AI6" s="22"/>
-      <c r="AJ6" s="22"/>
-      <c r="AK6" s="22"/>
-      <c r="AL6" s="22"/>
-      <c r="AM6" s="22"/>
+      <c r="T6" s="27"/>
+      <c r="U6" s="27"/>
+      <c r="V6" s="27"/>
+      <c r="W6" s="27"/>
+      <c r="X6" s="27"/>
+      <c r="Y6" s="27"/>
+      <c r="Z6" s="27"/>
+      <c r="AA6" s="27"/>
+      <c r="AB6" s="27"/>
+      <c r="AC6" s="27"/>
+      <c r="AD6" s="27"/>
+      <c r="AE6" s="27"/>
+      <c r="AF6" s="27"/>
+      <c r="AG6" s="27"/>
+      <c r="AH6" s="27"/>
+      <c r="AI6" s="27"/>
+      <c r="AJ6" s="27"/>
+      <c r="AK6" s="27"/>
+      <c r="AL6" s="27"/>
+      <c r="AM6" s="27"/>
+      <c r="AN6" s="27"/>
+      <c r="AO6" s="27"/>
+      <c r="AP6" s="27"/>
+      <c r="AQ6" s="27"/>
+      <c r="AR6" s="27"/>
+      <c r="AS6" s="27"/>
+      <c r="AT6" s="27"/>
+      <c r="AU6" s="27"/>
+      <c r="AV6" s="27"/>
+      <c r="AW6" s="27"/>
+      <c r="AX6" s="27"/>
+      <c r="AY6" s="27"/>
+      <c r="AZ6" s="27"/>
+      <c r="BA6" s="27"/>
+      <c r="BB6" s="27"/>
+      <c r="BC6" s="27"/>
+      <c r="BD6" s="27"/>
+      <c r="BE6" s="27"/>
+      <c r="BF6" s="27"/>
+      <c r="BG6" s="27"/>
+      <c r="BH6" s="27"/>
+      <c r="BI6" s="27"/>
+      <c r="BJ6" s="27"/>
+      <c r="BK6" s="28"/>
     </row>
-    <row r="7" spans="2:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
-      <c r="G7" t="s">
+      <c r="C7" s="27"/>
+      <c r="D7" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="20"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="27" t="s">
         <v>9</v>
       </c>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="27"/>
+      <c r="T7" s="27"/>
+      <c r="U7" s="27"/>
+      <c r="V7" s="27"/>
+      <c r="W7" s="27"/>
+      <c r="X7" s="27"/>
+      <c r="Y7" s="27"/>
+      <c r="Z7" s="27"/>
+      <c r="AA7" s="27"/>
+      <c r="AB7" s="27"/>
+      <c r="AC7" s="27"/>
+      <c r="AD7" s="27"/>
+      <c r="AE7" s="27"/>
+      <c r="AF7" s="27"/>
+      <c r="AG7" s="27"/>
+      <c r="AH7" s="27"/>
+      <c r="AI7" s="27"/>
+      <c r="AJ7" s="27"/>
+      <c r="AK7" s="27"/>
+      <c r="AL7" s="27"/>
+      <c r="AM7" s="27"/>
+      <c r="AN7" s="27"/>
+      <c r="AO7" s="27"/>
+      <c r="AP7" s="27"/>
+      <c r="AQ7" s="27"/>
+      <c r="AR7" s="27"/>
+      <c r="AS7" s="27"/>
+      <c r="AT7" s="27"/>
+      <c r="AU7" s="27"/>
+      <c r="AV7" s="27"/>
+      <c r="AW7" s="27"/>
+      <c r="AX7" s="27"/>
+      <c r="AY7" s="27"/>
+      <c r="AZ7" s="27"/>
+      <c r="BA7" s="27"/>
+      <c r="BB7" s="27"/>
+      <c r="BC7" s="27"/>
+      <c r="BD7" s="27"/>
+      <c r="BE7" s="27"/>
+      <c r="BF7" s="27"/>
+      <c r="BG7" s="27"/>
+      <c r="BH7" s="27"/>
+      <c r="BI7" s="27"/>
+      <c r="BJ7" s="27"/>
+      <c r="BK7" s="28"/>
     </row>
-    <row r="8" spans="2:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="AB8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC8" s="8"/>
-      <c r="AD8" s="22" t="s">
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="27"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="27"/>
+      <c r="V8" s="27"/>
+      <c r="W8" s="27"/>
+      <c r="X8" s="27"/>
+      <c r="Y8" s="27"/>
+      <c r="Z8" s="27"/>
+      <c r="AA8" s="27"/>
+      <c r="AB8" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC8" s="21"/>
+      <c r="AD8" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="AE8" s="22"/>
-      <c r="AF8" s="22"/>
-      <c r="AG8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH8" s="7"/>
-      <c r="AI8" s="7"/>
-      <c r="AJ8" s="7"/>
-      <c r="AK8" s="8"/>
-      <c r="AL8" s="22" t="s">
+      <c r="AE8" s="27"/>
+      <c r="AF8" s="27"/>
+      <c r="AG8" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH8" s="20"/>
+      <c r="AI8" s="20"/>
+      <c r="AJ8" s="20"/>
+      <c r="AK8" s="21"/>
+      <c r="AL8" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="AM8" s="22"/>
+      <c r="AM8" s="27"/>
+      <c r="AN8" s="27"/>
+      <c r="AO8" s="27"/>
       <c r="AP8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AQ8" t="s">
+      <c r="AQ8" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="AR8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS8" s="7"/>
-      <c r="AT8" s="7"/>
-      <c r="AU8" s="8"/>
-      <c r="AV8" t="s">
+      <c r="AR8" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS8" s="20"/>
+      <c r="AT8" s="20"/>
+      <c r="AU8" s="21"/>
+      <c r="AV8" s="27" t="s">
         <v>9</v>
       </c>
+      <c r="AW8" s="27"/>
+      <c r="AX8" s="27"/>
+      <c r="AY8" s="27"/>
+      <c r="AZ8" s="27"/>
+      <c r="BA8" s="27"/>
+      <c r="BB8" s="27"/>
+      <c r="BC8" s="27"/>
+      <c r="BD8" s="27"/>
+      <c r="BE8" s="27"/>
+      <c r="BF8" s="27"/>
+      <c r="BG8" s="27"/>
+      <c r="BH8" s="27"/>
+      <c r="BI8" s="27"/>
+      <c r="BJ8" s="27"/>
+      <c r="BK8" s="28"/>
     </row>
-    <row r="9" spans="2:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
       <c r="C9" s="1">
         <v>0</v>
@@ -1143,8 +1757,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="2:63" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
@@ -1183,122 +1797,122 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="2:63" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:63" x14ac:dyDescent="0.3">
-      <c r="B13" s="12" t="s">
+    <row r="12" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B13" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G13" s="9" t="s">
+      <c r="C13" s="9"/>
+      <c r="D13" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="K13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="M13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="N13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="O13" s="9" t="s">
+      <c r="O13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="P13" s="9" t="s">
+      <c r="P13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="Q13" s="9" t="s">
+      <c r="Q13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="R13" s="9" t="s">
+      <c r="R13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="S13" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="T13" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="U13" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="V13" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="W13" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="X13" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA13" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB13" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC13" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD13" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE13" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF13" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG13" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="AH13" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="AI13" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ13" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK13" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL13" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM13" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN13" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO13" s="23" t="s">
+      <c r="S13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="T13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="U13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="V13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="W13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="X13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AH13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO13" s="6" t="s">
         <v>5</v>
       </c>
       <c r="AP13" s="4"/>
@@ -1324,406 +1938,4492 @@
       <c r="BJ13" s="4"/>
       <c r="BK13" s="5"/>
     </row>
-    <row r="14" spans="2:63" x14ac:dyDescent="0.3">
-      <c r="B14" s="13"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="N14" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="O14" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="P14" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q14" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="R14" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="S14" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="T14" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="U14" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="V14" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="W14" s="10"/>
-      <c r="X14" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y14" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="10"/>
-      <c r="AA14" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB14" s="10"/>
-      <c r="AC14" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD14" s="10"/>
-      <c r="AE14" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF14" s="10"/>
-      <c r="AG14" s="10"/>
-      <c r="AH14" s="10"/>
-      <c r="AI14" s="10"/>
-      <c r="AJ14" s="10"/>
-      <c r="AK14" s="10"/>
-      <c r="AL14" s="10"/>
-      <c r="AM14" s="10"/>
-      <c r="AN14" s="18"/>
-      <c r="AO14" s="18"/>
-      <c r="AP14" s="18"/>
-      <c r="AQ14" s="18"/>
-      <c r="AR14" s="18"/>
-      <c r="AS14" s="18"/>
-      <c r="AT14" s="18"/>
-      <c r="AU14" s="18"/>
-      <c r="AV14" s="18"/>
-      <c r="AW14" s="18"/>
-      <c r="AX14" s="18"/>
-      <c r="AY14" s="18"/>
-      <c r="AZ14" s="18"/>
-      <c r="BA14" s="18"/>
-      <c r="BB14" s="18"/>
-      <c r="BC14" s="18"/>
-      <c r="BD14" s="18"/>
-      <c r="BE14" s="18"/>
-      <c r="BF14" s="18"/>
-      <c r="BG14" s="18"/>
-      <c r="BH14" s="18"/>
-      <c r="BI14" s="18"/>
-      <c r="BJ14" s="18"/>
-      <c r="BK14" s="24"/>
+    <row r="14" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B14" s="23"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="R14" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="S14" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="V14" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="7"/>
+      <c r="AA14" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB14" s="7"/>
+      <c r="AC14" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="7"/>
+      <c r="AE14" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF14" s="7"/>
+      <c r="AG14" s="7"/>
+      <c r="AH14" s="7"/>
+      <c r="AI14" s="7"/>
+      <c r="AJ14" s="7"/>
+      <c r="AK14" s="7"/>
+      <c r="AL14" s="7"/>
+      <c r="AM14" s="7"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+      <c r="BI14" s="12"/>
+      <c r="BJ14" s="12"/>
+      <c r="BK14" s="16"/>
     </row>
-    <row r="15" spans="2:63" x14ac:dyDescent="0.3">
-      <c r="B15" s="13"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="O15" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
-      <c r="V15" s="10"/>
-      <c r="W15" s="10"/>
-      <c r="X15" s="10"/>
-      <c r="Y15" s="10"/>
-      <c r="Z15" s="10"/>
-      <c r="AA15" s="10"/>
-      <c r="AB15" s="10"/>
-      <c r="AC15" s="10"/>
-      <c r="AD15" s="10"/>
-      <c r="AE15" s="10"/>
-      <c r="AF15" s="10"/>
-      <c r="AG15" s="10"/>
-      <c r="AH15" s="10"/>
-      <c r="AI15" s="10"/>
-      <c r="AJ15" s="18"/>
-      <c r="AK15" s="18"/>
-      <c r="AL15" s="18"/>
-      <c r="AM15" s="18"/>
-      <c r="AN15" s="18"/>
-      <c r="AO15" s="18"/>
-      <c r="AP15" s="18"/>
-      <c r="AQ15" s="18"/>
-      <c r="AR15" s="18"/>
-      <c r="AS15" s="18"/>
-      <c r="AT15" s="18"/>
-      <c r="AU15" s="18"/>
-      <c r="AV15" s="18"/>
-      <c r="AW15" s="18"/>
-      <c r="AX15" s="18"/>
-      <c r="AY15" s="18"/>
-      <c r="AZ15" s="18"/>
-      <c r="BA15" s="18"/>
-      <c r="BB15" s="18"/>
-      <c r="BC15" s="18"/>
-      <c r="BD15" s="18"/>
-      <c r="BE15" s="18"/>
-      <c r="BF15" s="18"/>
-      <c r="BG15" s="18"/>
-      <c r="BH15" s="18"/>
-      <c r="BI15" s="18"/>
-      <c r="BJ15" s="18"/>
-      <c r="BK15" s="24"/>
+    <row r="15" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B15" s="23"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7"/>
+      <c r="AA15" s="7"/>
+      <c r="AB15" s="7"/>
+      <c r="AC15" s="7"/>
+      <c r="AD15" s="7"/>
+      <c r="AE15" s="7"/>
+      <c r="AF15" s="7"/>
+      <c r="AG15" s="7"/>
+      <c r="AH15" s="7"/>
+      <c r="AI15" s="7"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+      <c r="BI15" s="12"/>
+      <c r="BJ15" s="12"/>
+      <c r="BK15" s="16"/>
     </row>
-    <row r="16" spans="2:63" x14ac:dyDescent="0.3">
-      <c r="B16" s="13"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
-      <c r="T16" s="10"/>
-      <c r="U16" s="10"/>
-      <c r="V16" s="10"/>
-      <c r="W16" s="10"/>
-      <c r="X16" s="10"/>
-      <c r="Y16" s="10"/>
-      <c r="Z16" s="10"/>
-      <c r="AA16" s="10"/>
-      <c r="AB16" s="10"/>
-      <c r="AC16" s="10"/>
-      <c r="AD16" s="10"/>
-      <c r="AE16" s="10"/>
-      <c r="AF16" s="10"/>
-      <c r="AG16" s="10"/>
-      <c r="AH16" s="10"/>
-      <c r="AI16" s="10"/>
-      <c r="AJ16" s="18"/>
-      <c r="AK16" s="18"/>
-      <c r="AL16" s="18"/>
-      <c r="AM16" s="18"/>
-      <c r="AN16" s="18"/>
-      <c r="AO16" s="18"/>
-      <c r="AP16" s="18"/>
-      <c r="AQ16" s="18"/>
-      <c r="AR16" s="18"/>
-      <c r="AS16" s="18"/>
-      <c r="AT16" s="18"/>
-      <c r="AU16" s="18"/>
-      <c r="AV16" s="18"/>
-      <c r="AW16" s="18"/>
-      <c r="AX16" s="18"/>
-      <c r="AY16" s="18"/>
-      <c r="AZ16" s="18"/>
-      <c r="BA16" s="18"/>
-      <c r="BB16" s="18"/>
-      <c r="BC16" s="18"/>
-      <c r="BD16" s="18"/>
-      <c r="BE16" s="18"/>
-      <c r="BF16" s="18"/>
-      <c r="BG16" s="18"/>
-      <c r="BH16" s="18"/>
-      <c r="BI16" s="18"/>
-      <c r="BJ16" s="18"/>
-      <c r="BK16" s="24"/>
+    <row r="16" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B16" s="23"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7"/>
+      <c r="AA16" s="7"/>
+      <c r="AB16" s="7"/>
+      <c r="AC16" s="7"/>
+      <c r="AD16" s="7"/>
+      <c r="AE16" s="7"/>
+      <c r="AF16" s="7"/>
+      <c r="AG16" s="7"/>
+      <c r="AH16" s="7"/>
+      <c r="AI16" s="7"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+      <c r="BI16" s="12"/>
+      <c r="BJ16" s="12"/>
+      <c r="BK16" s="16"/>
     </row>
-    <row r="17" spans="2:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="14"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="11"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="11"/>
-      <c r="Y17" s="11"/>
-      <c r="Z17" s="11"/>
-      <c r="AA17" s="11"/>
-      <c r="AB17" s="11"/>
-      <c r="AC17" s="11"/>
-      <c r="AD17" s="11"/>
-      <c r="AE17" s="11"/>
-      <c r="AF17" s="11"/>
-      <c r="AG17" s="11"/>
-      <c r="AH17" s="11"/>
-      <c r="AI17" s="11"/>
-      <c r="AJ17" s="25"/>
-      <c r="AK17" s="25"/>
-      <c r="AL17" s="25"/>
-      <c r="AM17" s="25"/>
-      <c r="AN17" s="25"/>
-      <c r="AO17" s="25"/>
-      <c r="AP17" s="25"/>
-      <c r="AQ17" s="25"/>
-      <c r="AR17" s="25"/>
-      <c r="AS17" s="25"/>
-      <c r="AT17" s="25"/>
-      <c r="AU17" s="25"/>
-      <c r="AV17" s="25"/>
-      <c r="AW17" s="25"/>
-      <c r="AX17" s="25"/>
-      <c r="AY17" s="25"/>
-      <c r="AZ17" s="25"/>
-      <c r="BA17" s="25"/>
-      <c r="BB17" s="25"/>
-      <c r="BC17" s="25"/>
-      <c r="BD17" s="25"/>
-      <c r="BE17" s="25"/>
-      <c r="BF17" s="25"/>
-      <c r="BG17" s="25"/>
-      <c r="BH17" s="25"/>
-      <c r="BI17" s="25"/>
-      <c r="BJ17" s="25"/>
-      <c r="BK17" s="26"/>
+    <row r="17" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="24"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="8"/>
+      <c r="X17" s="8"/>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="8"/>
+      <c r="AA17" s="8"/>
+      <c r="AB17" s="8"/>
+      <c r="AC17" s="8"/>
+      <c r="AD17" s="8"/>
+      <c r="AE17" s="8"/>
+      <c r="AF17" s="8"/>
+      <c r="AG17" s="8"/>
+      <c r="AH17" s="8"/>
+      <c r="AI17" s="8"/>
+      <c r="AJ17" s="17"/>
+      <c r="AK17" s="17"/>
+      <c r="AL17" s="17"/>
+      <c r="AM17" s="17"/>
+      <c r="AN17" s="17"/>
+      <c r="AO17" s="17"/>
+      <c r="AP17" s="17"/>
+      <c r="AQ17" s="17"/>
+      <c r="AR17" s="17"/>
+      <c r="AS17" s="17"/>
+      <c r="AT17" s="17"/>
+      <c r="AU17" s="17"/>
+      <c r="AV17" s="17"/>
+      <c r="AW17" s="17"/>
+      <c r="AX17" s="17"/>
+      <c r="AY17" s="17"/>
+      <c r="AZ17" s="17"/>
+      <c r="BA17" s="17"/>
+      <c r="BB17" s="17"/>
+      <c r="BC17" s="17"/>
+      <c r="BD17" s="17"/>
+      <c r="BE17" s="17"/>
+      <c r="BF17" s="17"/>
+      <c r="BG17" s="17"/>
+      <c r="BH17" s="17"/>
+      <c r="BI17" s="17"/>
+      <c r="BJ17" s="17"/>
+      <c r="BK17" s="18"/>
     </row>
-    <row r="18" spans="2:63" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="2:63" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="19" t="s">
+    <row r="18" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="20"/>
-      <c r="S19" s="20"/>
-      <c r="T19" s="20"/>
-      <c r="U19" s="20"/>
-      <c r="V19" s="20"/>
-      <c r="W19" s="20"/>
-      <c r="X19" s="20"/>
-      <c r="Y19" s="20"/>
-      <c r="Z19" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA19" s="20"/>
-      <c r="AB19" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC19" s="20"/>
-      <c r="AD19" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE19" s="20"/>
-      <c r="AF19" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG19" s="20"/>
-      <c r="AH19" s="20"/>
-      <c r="AI19" s="20"/>
-      <c r="AJ19" s="20"/>
-      <c r="AK19" s="20"/>
-      <c r="AL19" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM19" s="20"/>
-      <c r="AN19" s="20"/>
-      <c r="AO19" s="20"/>
-      <c r="AP19" s="20"/>
-      <c r="AQ19" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="AR19" s="20"/>
-      <c r="AS19" s="20"/>
-      <c r="AT19" s="20"/>
-      <c r="AU19" s="20"/>
-      <c r="AV19" s="20"/>
-      <c r="AW19" s="20"/>
-      <c r="AX19" s="20"/>
-      <c r="AY19" s="20"/>
-      <c r="AZ19" s="20"/>
-      <c r="BA19" s="20"/>
-      <c r="BB19" s="20"/>
-      <c r="BC19" s="20"/>
-      <c r="BD19" s="20"/>
-      <c r="BE19" s="20"/>
-      <c r="BF19" s="20"/>
-      <c r="BG19" s="20"/>
-      <c r="BH19" s="20"/>
-      <c r="BI19" s="20"/>
-      <c r="BJ19" s="20"/>
-      <c r="BK19" s="21"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14"/>
+      <c r="Q19" s="14"/>
+      <c r="R19" s="14"/>
+      <c r="S19" s="14"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="14"/>
+      <c r="V19" s="14"/>
+      <c r="W19" s="14"/>
+      <c r="X19" s="14"/>
+      <c r="Y19" s="14"/>
+      <c r="Z19" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA19" s="14"/>
+      <c r="AB19" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="14"/>
+      <c r="AD19" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE19" s="14"/>
+      <c r="AF19" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG19" s="14"/>
+      <c r="AH19" s="14"/>
+      <c r="AI19" s="14"/>
+      <c r="AJ19" s="14"/>
+      <c r="AK19" s="14"/>
+      <c r="AL19" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM19" s="14"/>
+      <c r="AN19" s="14"/>
+      <c r="AO19" s="14"/>
+      <c r="AP19" s="14"/>
+      <c r="AQ19" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="AR19" s="14"/>
+      <c r="AS19" s="14"/>
+      <c r="AT19" s="14"/>
+      <c r="AU19" s="14"/>
+      <c r="AV19" s="14"/>
+      <c r="AW19" s="14"/>
+      <c r="AX19" s="14"/>
+      <c r="AY19" s="14"/>
+      <c r="AZ19" s="14"/>
+      <c r="BA19" s="14"/>
+      <c r="BB19" s="14"/>
+      <c r="BC19" s="14"/>
+      <c r="BD19" s="14"/>
+      <c r="BE19" s="14"/>
+      <c r="BF19" s="14"/>
+      <c r="BG19" s="14"/>
+      <c r="BH19" s="14"/>
+      <c r="BI19" s="14"/>
+      <c r="BJ19" s="14"/>
+      <c r="BK19" s="15"/>
+    </row>
+    <row r="23" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="33"/>
+      <c r="S25" s="33"/>
+      <c r="T25" s="33"/>
+      <c r="U25" s="33"/>
+      <c r="V25" s="33"/>
+      <c r="W25" s="33"/>
+      <c r="X25" s="33"/>
+      <c r="Y25" s="33"/>
+      <c r="Z25" s="33"/>
+      <c r="AA25" s="33"/>
+      <c r="AB25" s="33"/>
+      <c r="AC25" s="33"/>
+      <c r="AD25" s="33"/>
+      <c r="AE25" s="33"/>
+      <c r="AF25" s="33"/>
+      <c r="AG25" s="33"/>
+      <c r="AH25" s="33"/>
+      <c r="AI25" s="33"/>
+      <c r="AJ25" s="33"/>
+      <c r="AK25" s="33"/>
+      <c r="AL25" s="33"/>
+      <c r="AM25" s="33"/>
+      <c r="AN25" s="33"/>
+      <c r="AO25" s="33"/>
+      <c r="AP25" s="33"/>
+      <c r="AQ25" s="33"/>
+      <c r="AR25" s="33"/>
+      <c r="AS25" s="33"/>
+      <c r="AT25" s="33"/>
+      <c r="AU25" s="33"/>
+      <c r="AV25" s="33"/>
+      <c r="AW25" s="33"/>
+      <c r="AX25" s="33"/>
+      <c r="AY25" s="33"/>
+      <c r="AZ25" s="33"/>
+      <c r="BA25" s="33"/>
+      <c r="BB25" s="33"/>
+      <c r="BC25" s="33"/>
+      <c r="BD25" s="33"/>
+      <c r="BE25" s="33"/>
+      <c r="BF25" s="33"/>
+      <c r="BG25" s="33"/>
+      <c r="BH25" s="33"/>
+      <c r="BI25" s="33"/>
+      <c r="BJ25" s="33"/>
+      <c r="BK25" s="34"/>
+    </row>
+    <row r="26" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="L26" s="46"/>
+      <c r="M26" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="N26" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="O26" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="P26" s="35"/>
+      <c r="Q26" s="35"/>
+      <c r="R26" s="35"/>
+      <c r="S26" s="35"/>
+      <c r="T26" s="35"/>
+      <c r="U26" s="35"/>
+      <c r="V26" s="35"/>
+      <c r="W26" s="35"/>
+      <c r="X26" s="35"/>
+      <c r="Y26" s="35"/>
+      <c r="Z26" s="35"/>
+      <c r="AA26" s="35"/>
+      <c r="AB26" s="35"/>
+      <c r="AC26" s="35"/>
+      <c r="AD26" s="35"/>
+      <c r="AE26" s="35"/>
+      <c r="AF26" s="35"/>
+      <c r="AG26" s="35"/>
+      <c r="AH26" s="35"/>
+      <c r="AI26" s="35"/>
+      <c r="AJ26" s="35"/>
+      <c r="AK26" s="35"/>
+      <c r="AL26" s="35"/>
+      <c r="AM26" s="35"/>
+      <c r="AN26" s="35"/>
+      <c r="AO26" s="35"/>
+      <c r="AP26" s="35"/>
+      <c r="AQ26" s="35"/>
+      <c r="AR26" s="35"/>
+      <c r="AS26" s="35"/>
+      <c r="AT26" s="35"/>
+      <c r="AU26" s="35"/>
+      <c r="AV26" s="35"/>
+      <c r="AW26" s="35"/>
+      <c r="AX26" s="35"/>
+      <c r="AY26" s="35"/>
+      <c r="AZ26" s="35"/>
+      <c r="BA26" s="35"/>
+      <c r="BB26" s="35"/>
+      <c r="BC26" s="35"/>
+      <c r="BD26" s="35"/>
+      <c r="BE26" s="35"/>
+      <c r="BF26" s="35"/>
+      <c r="BG26" s="35"/>
+      <c r="BH26" s="35"/>
+      <c r="BI26" s="35"/>
+      <c r="BJ26" s="35"/>
+      <c r="BK26" s="36"/>
+    </row>
+    <row r="27" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="N27" s="35"/>
+      <c r="O27" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="P27" s="49"/>
+      <c r="Q27" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R27" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="S27" s="49"/>
+      <c r="T27" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="U27" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="V27" s="50"/>
+      <c r="W27" s="50"/>
+      <c r="X27" s="49"/>
+      <c r="Y27" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z27" s="35"/>
+      <c r="AA27" s="35"/>
+      <c r="AB27" s="35"/>
+      <c r="AC27" s="35"/>
+      <c r="AD27" s="35"/>
+      <c r="AE27" s="35"/>
+      <c r="AF27" s="35"/>
+      <c r="AG27" s="35"/>
+      <c r="AH27" s="35"/>
+      <c r="AI27" s="35"/>
+      <c r="AJ27" s="35"/>
+      <c r="AK27" s="35"/>
+      <c r="AL27" s="35"/>
+      <c r="AM27" s="35"/>
+      <c r="AN27" s="35"/>
+      <c r="AO27" s="35"/>
+      <c r="AP27" s="35"/>
+      <c r="AQ27" s="35"/>
+      <c r="AR27" s="35"/>
+      <c r="AS27" s="35"/>
+      <c r="AT27" s="35"/>
+      <c r="AU27" s="35"/>
+      <c r="AV27" s="35"/>
+      <c r="AW27" s="35"/>
+      <c r="AX27" s="35"/>
+      <c r="AY27" s="35"/>
+      <c r="AZ27" s="35"/>
+      <c r="BA27" s="35"/>
+      <c r="BB27" s="35"/>
+      <c r="BC27" s="35"/>
+      <c r="BD27" s="35"/>
+      <c r="BE27" s="35"/>
+      <c r="BF27" s="35"/>
+      <c r="BG27" s="35"/>
+      <c r="BH27" s="35"/>
+      <c r="BI27" s="35"/>
+      <c r="BJ27" s="35"/>
+      <c r="BK27" s="36"/>
+    </row>
+    <row r="28" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="35"/>
+      <c r="D28" s="52" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" s="53"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="35"/>
+      <c r="P28" s="35"/>
+      <c r="Q28" s="35"/>
+      <c r="R28" s="35"/>
+      <c r="S28" s="35"/>
+      <c r="T28" s="35"/>
+      <c r="U28" s="35"/>
+      <c r="V28" s="35"/>
+      <c r="W28" s="35"/>
+      <c r="X28" s="35"/>
+      <c r="Y28" s="35"/>
+      <c r="Z28" s="35"/>
+      <c r="AA28" s="35"/>
+      <c r="AB28" s="35"/>
+      <c r="AC28" s="35"/>
+      <c r="AD28" s="35"/>
+      <c r="AE28" s="35"/>
+      <c r="AF28" s="52" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG28" s="54"/>
+      <c r="AH28" s="54"/>
+      <c r="AI28" s="54"/>
+      <c r="AJ28" s="54"/>
+      <c r="AK28" s="54"/>
+      <c r="AL28" s="54"/>
+      <c r="AM28" s="54"/>
+      <c r="AN28" s="54"/>
+      <c r="AO28" s="53"/>
+      <c r="AP28" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ28" s="35"/>
+      <c r="AR28" s="35"/>
+      <c r="AS28" s="35"/>
+      <c r="AT28" s="35"/>
+      <c r="AU28" s="35"/>
+      <c r="AV28" s="35"/>
+      <c r="AW28" s="35"/>
+      <c r="AX28" s="35"/>
+      <c r="AY28" s="35"/>
+      <c r="AZ28" s="35"/>
+      <c r="BA28" s="35"/>
+      <c r="BB28" s="35"/>
+      <c r="BC28" s="35"/>
+      <c r="BD28" s="35"/>
+      <c r="BE28" s="35"/>
+      <c r="BF28" s="35"/>
+      <c r="BG28" s="35"/>
+      <c r="BH28" s="35"/>
+      <c r="BI28" s="35"/>
+      <c r="BJ28" s="35"/>
+      <c r="BK28" s="36"/>
+    </row>
+    <row r="29" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="35"/>
+      <c r="P29" s="35"/>
+      <c r="Q29" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="35"/>
+      <c r="S29" s="35"/>
+      <c r="T29" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="U29" s="35"/>
+      <c r="V29" s="35"/>
+      <c r="W29" s="35"/>
+      <c r="X29" s="35"/>
+      <c r="Y29" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z29" s="57"/>
+      <c r="AA29" s="57"/>
+      <c r="AB29" s="57"/>
+      <c r="AC29" s="57"/>
+      <c r="AD29" s="57"/>
+      <c r="AE29" s="58"/>
+      <c r="AF29" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG29" s="35"/>
+      <c r="AH29" s="35"/>
+      <c r="AI29" s="35"/>
+      <c r="AJ29" s="35"/>
+      <c r="AK29" s="35"/>
+      <c r="AL29" s="35"/>
+      <c r="AM29" s="35"/>
+      <c r="AN29" s="35"/>
+      <c r="AO29" s="35"/>
+      <c r="AP29" s="35"/>
+      <c r="AQ29" s="35"/>
+      <c r="AR29" s="35"/>
+      <c r="AS29" s="35"/>
+      <c r="AT29" s="35"/>
+      <c r="AU29" s="35"/>
+      <c r="AV29" s="35"/>
+      <c r="AW29" s="35"/>
+      <c r="AX29" s="35"/>
+      <c r="AY29" s="35"/>
+      <c r="AZ29" s="35"/>
+      <c r="BA29" s="35"/>
+      <c r="BB29" s="35"/>
+      <c r="BC29" s="35"/>
+      <c r="BD29" s="35"/>
+      <c r="BE29" s="35"/>
+      <c r="BF29" s="35"/>
+      <c r="BG29" s="35"/>
+      <c r="BH29" s="35"/>
+      <c r="BI29" s="35"/>
+      <c r="BJ29" s="35"/>
+      <c r="BK29" s="36"/>
+    </row>
+    <row r="30" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
+      <c r="N30" s="35"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="35"/>
+      <c r="R30" s="35"/>
+      <c r="S30" s="35"/>
+      <c r="T30" s="35"/>
+      <c r="U30" s="35"/>
+      <c r="V30" s="35"/>
+      <c r="W30" s="35"/>
+      <c r="X30" s="35"/>
+      <c r="Y30" s="35"/>
+      <c r="Z30" s="35"/>
+      <c r="AA30" s="35"/>
+      <c r="AB30" s="35"/>
+      <c r="AC30" s="35"/>
+      <c r="AD30" s="35"/>
+      <c r="AE30" s="35"/>
+      <c r="AF30" s="35"/>
+      <c r="AG30" s="35"/>
+      <c r="AH30" s="35"/>
+      <c r="AI30" s="35"/>
+      <c r="AJ30" s="35"/>
+      <c r="AK30" s="35"/>
+      <c r="AL30" s="35"/>
+      <c r="AM30" s="35"/>
+      <c r="AN30" s="35"/>
+      <c r="AO30" s="35"/>
+      <c r="AP30" s="60" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ30" s="61"/>
+      <c r="AR30" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS30" s="60" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT30" s="62"/>
+      <c r="AU30" s="62"/>
+      <c r="AV30" s="62"/>
+      <c r="AW30" s="61"/>
+      <c r="AX30" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY30" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ30" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="BA30" s="60" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB30" s="62"/>
+      <c r="BC30" s="62"/>
+      <c r="BD30" s="61"/>
+      <c r="BE30" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF30" s="35"/>
+      <c r="BG30" s="35"/>
+      <c r="BH30" s="35"/>
+      <c r="BI30" s="35"/>
+      <c r="BJ30" s="35"/>
+      <c r="BK30" s="36"/>
+    </row>
+    <row r="31" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="39"/>
+      <c r="C31" s="39">
+        <v>0</v>
+      </c>
+      <c r="D31" s="39">
+        <v>1</v>
+      </c>
+      <c r="E31" s="39">
+        <v>2</v>
+      </c>
+      <c r="F31" s="39">
+        <v>3</v>
+      </c>
+      <c r="G31" s="39">
+        <v>4</v>
+      </c>
+      <c r="H31" s="39">
+        <v>5</v>
+      </c>
+      <c r="I31" s="39">
+        <v>6</v>
+      </c>
+      <c r="J31" s="39">
+        <v>7</v>
+      </c>
+      <c r="K31" s="39">
+        <v>8</v>
+      </c>
+      <c r="L31" s="39">
+        <v>9</v>
+      </c>
+      <c r="M31" s="39">
+        <v>10</v>
+      </c>
+      <c r="N31" s="39">
+        <v>11</v>
+      </c>
+      <c r="O31" s="39">
+        <v>12</v>
+      </c>
+      <c r="P31" s="39">
+        <v>13</v>
+      </c>
+      <c r="Q31" s="39">
+        <v>14</v>
+      </c>
+      <c r="R31" s="39">
+        <v>15</v>
+      </c>
+      <c r="S31" s="39">
+        <v>16</v>
+      </c>
+      <c r="T31" s="39">
+        <v>17</v>
+      </c>
+      <c r="U31" s="39">
+        <v>18</v>
+      </c>
+      <c r="V31" s="39">
+        <v>19</v>
+      </c>
+      <c r="W31" s="39">
+        <v>20</v>
+      </c>
+      <c r="X31" s="39">
+        <v>21</v>
+      </c>
+      <c r="Y31" s="39">
+        <v>22</v>
+      </c>
+      <c r="Z31" s="39">
+        <v>23</v>
+      </c>
+      <c r="AA31" s="39">
+        <v>24</v>
+      </c>
+      <c r="AB31" s="39">
+        <v>25</v>
+      </c>
+      <c r="AC31" s="39">
+        <v>26</v>
+      </c>
+      <c r="AD31" s="39">
+        <v>27</v>
+      </c>
+      <c r="AE31" s="39">
+        <v>28</v>
+      </c>
+      <c r="AF31" s="39">
+        <v>29</v>
+      </c>
+      <c r="AG31" s="39">
+        <v>30</v>
+      </c>
+      <c r="AH31" s="39">
+        <v>31</v>
+      </c>
+      <c r="AI31" s="39">
+        <v>32</v>
+      </c>
+      <c r="AJ31" s="39">
+        <v>33</v>
+      </c>
+      <c r="AK31" s="39">
+        <v>34</v>
+      </c>
+      <c r="AL31" s="39">
+        <v>35</v>
+      </c>
+      <c r="AM31" s="39">
+        <v>36</v>
+      </c>
+      <c r="AN31" s="39">
+        <v>37</v>
+      </c>
+      <c r="AO31" s="39">
+        <v>38</v>
+      </c>
+      <c r="AP31" s="39">
+        <v>39</v>
+      </c>
+      <c r="AQ31" s="39">
+        <v>40</v>
+      </c>
+      <c r="AR31" s="39">
+        <v>41</v>
+      </c>
+      <c r="AS31" s="39">
+        <v>42</v>
+      </c>
+      <c r="AT31" s="39">
+        <v>43</v>
+      </c>
+      <c r="AU31" s="39">
+        <v>44</v>
+      </c>
+      <c r="AV31" s="39">
+        <v>45</v>
+      </c>
+      <c r="AW31" s="39">
+        <v>46</v>
+      </c>
+      <c r="AX31" s="39">
+        <v>47</v>
+      </c>
+      <c r="AY31" s="39">
+        <v>48</v>
+      </c>
+      <c r="AZ31" s="39">
+        <v>49</v>
+      </c>
+      <c r="BA31" s="39">
+        <v>50</v>
+      </c>
+      <c r="BB31" s="39">
+        <v>51</v>
+      </c>
+      <c r="BC31" s="39">
+        <v>52</v>
+      </c>
+      <c r="BD31" s="39">
+        <v>53</v>
+      </c>
+      <c r="BE31" s="39">
+        <v>54</v>
+      </c>
+      <c r="BF31" s="39">
+        <v>55</v>
+      </c>
+      <c r="BG31" s="39">
+        <v>56</v>
+      </c>
+      <c r="BH31" s="39">
+        <v>57</v>
+      </c>
+      <c r="BI31" s="39">
+        <v>58</v>
+      </c>
+      <c r="BJ31" s="39">
+        <v>59</v>
+      </c>
+      <c r="BK31" s="39">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="33" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="2:68" x14ac:dyDescent="0.25">
+      <c r="B35" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N35" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O35" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="T35" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="V35" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="W35" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="X35" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y35" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z35" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA35" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB35" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC35" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD35" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE35" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF35" s="6"/>
+      <c r="AG35" s="6"/>
+      <c r="AH35" s="6"/>
+      <c r="AI35" s="6"/>
+      <c r="AJ35" s="6"/>
+      <c r="AK35" s="6"/>
+      <c r="AL35" s="6"/>
+      <c r="AM35" s="6"/>
+      <c r="AN35" s="6"/>
+      <c r="AO35" s="6"/>
+      <c r="AP35" s="4"/>
+      <c r="AQ35" s="4"/>
+      <c r="AR35" s="4"/>
+      <c r="AS35" s="4"/>
+      <c r="AT35" s="4"/>
+      <c r="AU35" s="4"/>
+      <c r="AV35" s="4"/>
+      <c r="AW35" s="4"/>
+      <c r="AX35" s="4"/>
+      <c r="AY35" s="4"/>
+      <c r="AZ35" s="4"/>
+      <c r="BA35" s="4"/>
+      <c r="BB35" s="4"/>
+      <c r="BC35" s="4"/>
+      <c r="BD35" s="4"/>
+      <c r="BE35" s="4"/>
+      <c r="BF35" s="4"/>
+      <c r="BG35" s="4"/>
+      <c r="BH35" s="4"/>
+      <c r="BI35" s="4"/>
+      <c r="BJ35" s="4"/>
+      <c r="BK35" s="5"/>
+    </row>
+    <row r="36" spans="2:68" x14ac:dyDescent="0.25">
+      <c r="B36" s="23"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="M36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="O36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="P36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="7"/>
+      <c r="R36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="S36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="T36" s="7"/>
+      <c r="U36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="V36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="W36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="X36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y36" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z36" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA36" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB36" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC36" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD36" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE36" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF36" s="7"/>
+      <c r="AG36" s="7"/>
+      <c r="AH36" s="7"/>
+      <c r="AI36" s="7"/>
+      <c r="AJ36" s="7"/>
+      <c r="AK36" s="7"/>
+      <c r="AL36" s="7"/>
+      <c r="AM36" s="7"/>
+      <c r="AN36" s="12"/>
+      <c r="AO36" s="12"/>
+      <c r="AP36" s="12"/>
+      <c r="AQ36" s="12"/>
+      <c r="AR36" s="12"/>
+      <c r="AS36" s="12"/>
+      <c r="AT36" s="12"/>
+      <c r="AU36" s="12"/>
+      <c r="AV36" s="12"/>
+      <c r="AW36" s="12"/>
+      <c r="AX36" s="12"/>
+      <c r="AY36" s="12"/>
+      <c r="AZ36" s="12"/>
+      <c r="BA36" s="12"/>
+      <c r="BB36" s="12"/>
+      <c r="BC36" s="12"/>
+      <c r="BD36" s="12"/>
+      <c r="BE36" s="12"/>
+      <c r="BF36" s="12"/>
+      <c r="BG36" s="12"/>
+      <c r="BH36" s="12"/>
+      <c r="BI36" s="12"/>
+      <c r="BJ36" s="12"/>
+      <c r="BK36" s="16"/>
+    </row>
+    <row r="37" spans="2:68" x14ac:dyDescent="0.25">
+      <c r="B37" s="23"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="M37" s="7"/>
+      <c r="N37" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="7"/>
+      <c r="S37" s="7"/>
+      <c r="T37" s="7"/>
+      <c r="U37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7"/>
+      <c r="X37" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y37" s="7"/>
+      <c r="Z37" s="7"/>
+      <c r="AA37" s="7"/>
+      <c r="AB37" s="7"/>
+      <c r="AC37" s="7"/>
+      <c r="AD37" s="7"/>
+      <c r="AE37" s="7"/>
+      <c r="AF37" s="7"/>
+      <c r="AG37" s="7"/>
+      <c r="AH37" s="7"/>
+      <c r="AI37" s="7"/>
+      <c r="AJ37" s="12"/>
+      <c r="AK37" s="12"/>
+      <c r="AL37" s="12"/>
+      <c r="AM37" s="12"/>
+      <c r="AN37" s="12"/>
+      <c r="AO37" s="12"/>
+      <c r="AP37" s="12"/>
+      <c r="AQ37" s="12"/>
+      <c r="AR37" s="12"/>
+      <c r="AS37" s="12"/>
+      <c r="AT37" s="12"/>
+      <c r="AU37" s="12"/>
+      <c r="AV37" s="12"/>
+      <c r="AW37" s="12"/>
+      <c r="AX37" s="12"/>
+      <c r="AY37" s="12"/>
+      <c r="AZ37" s="12"/>
+      <c r="BA37" s="12"/>
+      <c r="BB37" s="12"/>
+      <c r="BC37" s="12"/>
+      <c r="BD37" s="12"/>
+      <c r="BE37" s="12"/>
+      <c r="BF37" s="12"/>
+      <c r="BG37" s="12"/>
+      <c r="BH37" s="12"/>
+      <c r="BI37" s="12"/>
+      <c r="BJ37" s="12"/>
+      <c r="BK37" s="16"/>
+    </row>
+    <row r="38" spans="2:68" x14ac:dyDescent="0.25">
+      <c r="B38" s="23"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
+      <c r="P38" s="7"/>
+      <c r="Q38" s="7"/>
+      <c r="R38" s="7"/>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+      <c r="U38" s="7"/>
+      <c r="V38" s="7"/>
+      <c r="W38" s="7"/>
+      <c r="X38" s="7"/>
+      <c r="Y38" s="7"/>
+      <c r="Z38" s="7"/>
+      <c r="AA38" s="7"/>
+      <c r="AB38" s="7"/>
+      <c r="AC38" s="7"/>
+      <c r="AD38" s="7"/>
+      <c r="AE38" s="7"/>
+      <c r="AF38" s="7"/>
+      <c r="AG38" s="7"/>
+      <c r="AH38" s="7"/>
+      <c r="AI38" s="7"/>
+      <c r="AJ38" s="12"/>
+      <c r="AK38" s="12"/>
+      <c r="AL38" s="12"/>
+      <c r="AM38" s="12"/>
+      <c r="AN38" s="12"/>
+      <c r="AO38" s="12"/>
+      <c r="AP38" s="12"/>
+      <c r="AQ38" s="12"/>
+      <c r="AR38" s="12"/>
+      <c r="AS38" s="12"/>
+      <c r="AT38" s="12"/>
+      <c r="AU38" s="12"/>
+      <c r="AV38" s="12"/>
+      <c r="AW38" s="12"/>
+      <c r="AX38" s="12"/>
+      <c r="AY38" s="12"/>
+      <c r="AZ38" s="12"/>
+      <c r="BA38" s="12"/>
+      <c r="BB38" s="12"/>
+      <c r="BC38" s="12"/>
+      <c r="BD38" s="12"/>
+      <c r="BE38" s="12"/>
+      <c r="BF38" s="12"/>
+      <c r="BG38" s="12"/>
+      <c r="BH38" s="12"/>
+      <c r="BI38" s="12"/>
+      <c r="BJ38" s="12"/>
+      <c r="BK38" s="16"/>
+    </row>
+    <row r="39" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="24"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8"/>
+      <c r="P39" s="8"/>
+      <c r="Q39" s="8"/>
+      <c r="R39" s="8"/>
+      <c r="S39" s="8"/>
+      <c r="T39" s="8"/>
+      <c r="U39" s="8"/>
+      <c r="V39" s="8"/>
+      <c r="W39" s="8"/>
+      <c r="X39" s="8"/>
+      <c r="Y39" s="8"/>
+      <c r="Z39" s="8"/>
+      <c r="AA39" s="8"/>
+      <c r="AB39" s="8"/>
+      <c r="AC39" s="8"/>
+      <c r="AD39" s="8"/>
+      <c r="AE39" s="8"/>
+      <c r="AF39" s="8"/>
+      <c r="AG39" s="8"/>
+      <c r="AH39" s="8"/>
+      <c r="AI39" s="8"/>
+      <c r="AJ39" s="17"/>
+      <c r="AK39" s="17"/>
+      <c r="AL39" s="17"/>
+      <c r="AM39" s="17"/>
+      <c r="AN39" s="17"/>
+      <c r="AO39" s="17"/>
+      <c r="AP39" s="17"/>
+      <c r="AQ39" s="17"/>
+      <c r="AR39" s="17"/>
+      <c r="AS39" s="17"/>
+      <c r="AT39" s="17"/>
+      <c r="AU39" s="17"/>
+      <c r="AV39" s="17"/>
+      <c r="AW39" s="17"/>
+      <c r="AX39" s="17"/>
+      <c r="AY39" s="17"/>
+      <c r="AZ39" s="17"/>
+      <c r="BA39" s="17"/>
+      <c r="BB39" s="17"/>
+      <c r="BC39" s="17"/>
+      <c r="BD39" s="17"/>
+      <c r="BE39" s="17"/>
+      <c r="BF39" s="17"/>
+      <c r="BG39" s="17"/>
+      <c r="BH39" s="17"/>
+      <c r="BI39" s="17"/>
+      <c r="BJ39" s="17"/>
+      <c r="BK39" s="18"/>
+    </row>
+    <row r="40" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="N41" s="14"/>
+      <c r="O41" s="14"/>
+      <c r="P41" s="14"/>
+      <c r="Q41" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="R41" s="14"/>
+      <c r="S41" s="14"/>
+      <c r="T41" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="U41" s="14"/>
+      <c r="V41" s="14"/>
+      <c r="W41" s="14"/>
+      <c r="X41" s="14"/>
+      <c r="Y41" s="14"/>
+      <c r="Z41" s="14"/>
+      <c r="AA41" s="14"/>
+      <c r="AB41" s="14"/>
+      <c r="AC41" s="14"/>
+      <c r="AD41" s="14"/>
+      <c r="AE41" s="14"/>
+      <c r="AF41" s="14"/>
+      <c r="AG41" s="14"/>
+      <c r="AH41" s="14"/>
+      <c r="AI41" s="14"/>
+      <c r="AJ41" s="14"/>
+      <c r="AK41" s="14"/>
+      <c r="AL41" s="14"/>
+      <c r="AM41" s="14"/>
+      <c r="AN41" s="14"/>
+      <c r="AO41" s="14"/>
+      <c r="AP41" s="14"/>
+      <c r="AQ41" s="14"/>
+      <c r="AR41" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS41" s="14"/>
+      <c r="AT41" s="14"/>
+      <c r="AU41" s="14"/>
+      <c r="AV41" s="14"/>
+      <c r="AW41" s="14"/>
+      <c r="AX41" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY41" s="14"/>
+      <c r="AZ41" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="BA41" s="14"/>
+      <c r="BB41" s="14"/>
+      <c r="BC41" s="14"/>
+      <c r="BD41" s="14"/>
+      <c r="BE41" s="14"/>
+      <c r="BF41" s="14"/>
+      <c r="BG41" s="14"/>
+      <c r="BH41" s="14"/>
+      <c r="BI41" s="14"/>
+      <c r="BJ41" s="14"/>
+      <c r="BK41" s="15"/>
+    </row>
+    <row r="44" spans="2:68" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="C46" s="33"/>
+      <c r="D46" s="33"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="H46" s="42"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="L46" s="33"/>
+      <c r="M46" s="33"/>
+      <c r="N46" s="33"/>
+      <c r="O46" s="33"/>
+      <c r="P46" s="33"/>
+      <c r="Q46" s="33"/>
+      <c r="R46" s="33"/>
+      <c r="S46" s="33"/>
+      <c r="T46" s="33"/>
+      <c r="U46" s="33"/>
+      <c r="V46" s="33"/>
+      <c r="W46" s="33"/>
+      <c r="X46" s="33"/>
+      <c r="Y46" s="33"/>
+      <c r="Z46" s="33"/>
+      <c r="AA46" s="33"/>
+      <c r="AB46" s="33"/>
+      <c r="AC46" s="33"/>
+      <c r="AD46" s="33"/>
+      <c r="AE46" s="33"/>
+      <c r="AF46" s="33"/>
+      <c r="AG46" s="33"/>
+      <c r="AH46" s="33"/>
+      <c r="AI46" s="33"/>
+      <c r="AJ46" s="33"/>
+      <c r="AK46" s="33"/>
+      <c r="AL46" s="33"/>
+      <c r="AM46" s="33"/>
+      <c r="AN46" s="33"/>
+      <c r="AO46" s="33"/>
+      <c r="AP46" s="33"/>
+      <c r="AQ46" s="33"/>
+      <c r="AR46" s="33"/>
+      <c r="AS46" s="33"/>
+      <c r="AT46" s="33"/>
+      <c r="AU46" s="33"/>
+      <c r="AV46" s="33"/>
+      <c r="AW46" s="33"/>
+      <c r="AX46" s="33"/>
+      <c r="AY46" s="33"/>
+      <c r="AZ46" s="33"/>
+      <c r="BA46" s="33"/>
+      <c r="BB46" s="33"/>
+      <c r="BC46" s="33"/>
+      <c r="BD46" s="33"/>
+      <c r="BE46" s="33"/>
+      <c r="BF46" s="33"/>
+      <c r="BG46" s="33"/>
+      <c r="BH46" s="33"/>
+      <c r="BI46" s="33"/>
+      <c r="BJ46" s="33"/>
+      <c r="BK46" s="34"/>
+      <c r="BM46" s="67"/>
+      <c r="BN46" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="BO46" s="67" t="s">
+        <v>19</v>
+      </c>
+      <c r="BP46" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
+      <c r="E47" s="35"/>
+      <c r="F47" s="35"/>
+      <c r="G47" s="35"/>
+      <c r="H47" s="35"/>
+      <c r="I47" s="35"/>
+      <c r="J47" s="35"/>
+      <c r="K47" s="35"/>
+      <c r="L47" s="35"/>
+      <c r="M47" s="35"/>
+      <c r="N47" s="35"/>
+      <c r="O47" s="35"/>
+      <c r="P47" s="35"/>
+      <c r="Q47" s="35"/>
+      <c r="R47" s="35"/>
+      <c r="S47" s="35"/>
+      <c r="T47" s="35"/>
+      <c r="U47" s="35"/>
+      <c r="V47" s="35"/>
+      <c r="W47" s="35"/>
+      <c r="X47" s="35"/>
+      <c r="Y47" s="35"/>
+      <c r="Z47" s="35"/>
+      <c r="AA47" s="35"/>
+      <c r="AB47" s="35"/>
+      <c r="AC47" s="35"/>
+      <c r="AD47" s="35"/>
+      <c r="AE47" s="35"/>
+      <c r="AF47" s="35"/>
+      <c r="AG47" s="35"/>
+      <c r="AH47" s="35"/>
+      <c r="AI47" s="35"/>
+      <c r="AJ47" s="35"/>
+      <c r="AK47" s="35"/>
+      <c r="AL47" s="35"/>
+      <c r="AM47" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN47" s="46"/>
+      <c r="AO47" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP47" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ47" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AR47" s="35"/>
+      <c r="AS47" s="35"/>
+      <c r="AT47" s="35"/>
+      <c r="AU47" s="35"/>
+      <c r="AV47" s="35"/>
+      <c r="AW47" s="35"/>
+      <c r="AX47" s="35"/>
+      <c r="AY47" s="35"/>
+      <c r="AZ47" s="35"/>
+      <c r="BA47" s="35"/>
+      <c r="BB47" s="35"/>
+      <c r="BC47" s="35"/>
+      <c r="BD47" s="35"/>
+      <c r="BE47" s="35"/>
+      <c r="BF47" s="35"/>
+      <c r="BG47" s="35"/>
+      <c r="BH47" s="35"/>
+      <c r="BI47" s="35"/>
+      <c r="BJ47" s="35"/>
+      <c r="BK47" s="36"/>
+      <c r="BM47" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="BN47" s="67">
+        <v>4</v>
+      </c>
+      <c r="BO47" s="67">
+        <v>0</v>
+      </c>
+      <c r="BP47">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="35"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="35"/>
+      <c r="F48" s="35"/>
+      <c r="G48" s="35"/>
+      <c r="H48" s="35"/>
+      <c r="I48" s="35"/>
+      <c r="J48" s="35"/>
+      <c r="K48" s="85" t="s">
+        <v>2</v>
+      </c>
+      <c r="L48" s="86"/>
+      <c r="M48" s="87"/>
+      <c r="N48" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="O48" s="85" t="s">
+        <v>2</v>
+      </c>
+      <c r="P48" s="87"/>
+      <c r="Q48" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="R48" s="85" t="s">
+        <v>2</v>
+      </c>
+      <c r="S48" s="86"/>
+      <c r="T48" s="86"/>
+      <c r="U48" s="87"/>
+      <c r="V48" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="W48" s="35"/>
+      <c r="X48" s="35"/>
+      <c r="Y48" s="35"/>
+      <c r="Z48" s="35"/>
+      <c r="AA48" s="35"/>
+      <c r="AB48" s="35"/>
+      <c r="AC48" s="35"/>
+      <c r="AD48" s="35"/>
+      <c r="AE48" s="35"/>
+      <c r="AF48" s="35"/>
+      <c r="AG48" s="35"/>
+      <c r="AH48" s="35"/>
+      <c r="AI48" s="35"/>
+      <c r="AJ48" s="35"/>
+      <c r="AK48" s="35"/>
+      <c r="AL48" s="35"/>
+      <c r="AM48" s="35"/>
+      <c r="AN48" s="35"/>
+      <c r="AO48" s="35"/>
+      <c r="AP48" s="35"/>
+      <c r="AQ48" s="35"/>
+      <c r="AR48" s="35"/>
+      <c r="AS48" s="35"/>
+      <c r="AT48" s="35"/>
+      <c r="AU48" s="35"/>
+      <c r="AV48" s="35"/>
+      <c r="AW48" s="35"/>
+      <c r="AX48" s="35"/>
+      <c r="AY48" s="35"/>
+      <c r="AZ48" s="35"/>
+      <c r="BA48" s="35"/>
+      <c r="BB48" s="35"/>
+      <c r="BC48" s="35"/>
+      <c r="BD48" s="35"/>
+      <c r="BE48" s="35"/>
+      <c r="BF48" s="35"/>
+      <c r="BG48" s="35"/>
+      <c r="BH48" s="35"/>
+      <c r="BI48" s="35"/>
+      <c r="BJ48" s="35"/>
+      <c r="BK48" s="36"/>
+      <c r="BM48" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN48" s="67">
+        <v>5</v>
+      </c>
+      <c r="BO48" s="67">
+        <v>1</v>
+      </c>
+      <c r="BP48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" s="35"/>
+      <c r="D49" s="52" t="s">
+        <v>3</v>
+      </c>
+      <c r="E49" s="54"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="H49" s="35"/>
+      <c r="I49" s="35"/>
+      <c r="J49" s="35"/>
+      <c r="K49" s="35"/>
+      <c r="L49" s="35"/>
+      <c r="M49" s="35"/>
+      <c r="N49" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="P49" s="35"/>
+      <c r="Q49" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="S49" s="35"/>
+      <c r="T49" s="35"/>
+      <c r="U49" s="35"/>
+      <c r="V49" s="52" t="s">
+        <v>3</v>
+      </c>
+      <c r="W49" s="54"/>
+      <c r="X49" s="54"/>
+      <c r="Y49" s="54"/>
+      <c r="Z49" s="54"/>
+      <c r="AA49" s="54"/>
+      <c r="AB49" s="53"/>
+      <c r="AC49" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD49" s="35"/>
+      <c r="AE49" s="35"/>
+      <c r="AF49" s="35"/>
+      <c r="AG49" s="35"/>
+      <c r="AH49" s="35"/>
+      <c r="AI49" s="35"/>
+      <c r="AJ49" s="35"/>
+      <c r="AK49" s="35"/>
+      <c r="AL49" s="35"/>
+      <c r="AM49" s="35"/>
+      <c r="AN49" s="35"/>
+      <c r="AO49" s="35"/>
+      <c r="AP49" s="35"/>
+      <c r="AQ49" s="35"/>
+      <c r="AR49" s="35"/>
+      <c r="AS49" s="35"/>
+      <c r="AT49" s="35"/>
+      <c r="AU49" s="35"/>
+      <c r="AV49" s="35"/>
+      <c r="AW49" s="35"/>
+      <c r="AX49" s="35"/>
+      <c r="AY49" s="35"/>
+      <c r="AZ49" s="35"/>
+      <c r="BA49" s="35"/>
+      <c r="BB49" s="35"/>
+      <c r="BC49" s="35"/>
+      <c r="BD49" s="35"/>
+      <c r="BE49" s="35"/>
+      <c r="BF49" s="35"/>
+      <c r="BG49" s="35"/>
+      <c r="BH49" s="35"/>
+      <c r="BI49" s="35"/>
+      <c r="BJ49" s="35"/>
+      <c r="BK49" s="36"/>
+      <c r="BM49" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="BN49" s="67">
+        <v>16</v>
+      </c>
+      <c r="BO49" s="67">
+        <v>7</v>
+      </c>
+      <c r="BP49">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" s="35"/>
+      <c r="D50" s="35"/>
+      <c r="E50" s="35"/>
+      <c r="F50" s="35"/>
+      <c r="G50" s="35"/>
+      <c r="H50" s="35"/>
+      <c r="I50" s="35"/>
+      <c r="J50" s="35"/>
+      <c r="K50" s="35"/>
+      <c r="L50" s="35"/>
+      <c r="M50" s="35"/>
+      <c r="N50" s="35"/>
+      <c r="O50" s="35"/>
+      <c r="P50" s="35"/>
+      <c r="Q50" s="35"/>
+      <c r="R50" s="35"/>
+      <c r="S50" s="35"/>
+      <c r="T50" s="35"/>
+      <c r="U50" s="35"/>
+      <c r="V50" s="35"/>
+      <c r="W50" s="35"/>
+      <c r="X50" s="35"/>
+      <c r="Y50" s="35"/>
+      <c r="Z50" s="35"/>
+      <c r="AA50" s="35"/>
+      <c r="AB50" s="35"/>
+      <c r="AC50" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD50" s="57"/>
+      <c r="AE50" s="57"/>
+      <c r="AF50" s="57"/>
+      <c r="AG50" s="57"/>
+      <c r="AH50" s="57"/>
+      <c r="AI50" s="57"/>
+      <c r="AJ50" s="57"/>
+      <c r="AK50" s="57"/>
+      <c r="AL50" s="58"/>
+      <c r="AM50" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN50" s="35"/>
+      <c r="AO50" s="35"/>
+      <c r="AP50" s="35"/>
+      <c r="AQ50" s="35"/>
+      <c r="AR50" s="35"/>
+      <c r="AS50" s="35"/>
+      <c r="AT50" s="35"/>
+      <c r="AU50" s="35"/>
+      <c r="AV50" s="35"/>
+      <c r="AW50" s="35"/>
+      <c r="AX50" s="35"/>
+      <c r="AY50" s="35"/>
+      <c r="AZ50" s="35"/>
+      <c r="BA50" s="35"/>
+      <c r="BB50" s="35"/>
+      <c r="BC50" s="35"/>
+      <c r="BD50" s="35"/>
+      <c r="BE50" s="35"/>
+      <c r="BF50" s="35"/>
+      <c r="BG50" s="35"/>
+      <c r="BH50" s="35"/>
+      <c r="BI50" s="35"/>
+      <c r="BJ50" s="35"/>
+      <c r="BK50" s="36"/>
+      <c r="BM50" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN50" s="67"/>
+      <c r="BO50" s="88"/>
+    </row>
+    <row r="51" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="37"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="37"/>
+      <c r="H51" s="37"/>
+      <c r="I51" s="37"/>
+      <c r="J51" s="37"/>
+      <c r="K51" s="37"/>
+      <c r="L51" s="37"/>
+      <c r="M51" s="37"/>
+      <c r="N51" s="37"/>
+      <c r="O51" s="37"/>
+      <c r="P51" s="37"/>
+      <c r="Q51" s="37"/>
+      <c r="R51" s="37"/>
+      <c r="S51" s="37"/>
+      <c r="T51" s="37"/>
+      <c r="U51" s="37"/>
+      <c r="V51" s="37"/>
+      <c r="W51" s="37"/>
+      <c r="X51" s="37"/>
+      <c r="Y51" s="37"/>
+      <c r="Z51" s="37"/>
+      <c r="AA51" s="37"/>
+      <c r="AB51" s="37"/>
+      <c r="AC51" s="37"/>
+      <c r="AD51" s="37"/>
+      <c r="AE51" s="37"/>
+      <c r="AF51" s="37"/>
+      <c r="AG51" s="37"/>
+      <c r="AH51" s="37"/>
+      <c r="AI51" s="37"/>
+      <c r="AJ51" s="37"/>
+      <c r="AK51" s="37"/>
+      <c r="AL51" s="37"/>
+      <c r="AM51" s="37"/>
+      <c r="AN51" s="37"/>
+      <c r="AO51" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP51" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ51" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="AR51" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS51" s="64" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT51" s="65"/>
+      <c r="AU51" s="65"/>
+      <c r="AV51" s="65"/>
+      <c r="AW51" s="66"/>
+      <c r="AX51" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY51" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ51" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="BA51" s="60" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB51" s="62"/>
+      <c r="BC51" s="62"/>
+      <c r="BD51" s="61"/>
+      <c r="BE51" s="35"/>
+      <c r="BF51" s="37"/>
+      <c r="BG51" s="37"/>
+      <c r="BH51" s="37"/>
+      <c r="BI51" s="37"/>
+      <c r="BJ51" s="37"/>
+      <c r="BK51" s="38"/>
+      <c r="BM51" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="BN51" s="67"/>
+      <c r="BO51" s="67"/>
+    </row>
+    <row r="52" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="2"/>
+      <c r="C52" s="2">
+        <v>0</v>
+      </c>
+      <c r="D52" s="2">
+        <v>1</v>
+      </c>
+      <c r="E52" s="2">
+        <v>2</v>
+      </c>
+      <c r="F52" s="2">
+        <v>3</v>
+      </c>
+      <c r="G52" s="2">
+        <v>4</v>
+      </c>
+      <c r="H52" s="2">
+        <v>5</v>
+      </c>
+      <c r="I52" s="2">
+        <v>6</v>
+      </c>
+      <c r="J52" s="2">
+        <v>7</v>
+      </c>
+      <c r="K52" s="2">
+        <v>8</v>
+      </c>
+      <c r="L52" s="2">
+        <v>9</v>
+      </c>
+      <c r="M52" s="2">
+        <v>10</v>
+      </c>
+      <c r="N52" s="2">
+        <v>11</v>
+      </c>
+      <c r="O52" s="2">
+        <v>12</v>
+      </c>
+      <c r="P52" s="2">
+        <v>13</v>
+      </c>
+      <c r="Q52" s="2">
+        <v>14</v>
+      </c>
+      <c r="R52" s="2">
+        <v>15</v>
+      </c>
+      <c r="S52" s="2">
+        <v>16</v>
+      </c>
+      <c r="T52" s="2">
+        <v>17</v>
+      </c>
+      <c r="U52" s="2">
+        <v>18</v>
+      </c>
+      <c r="V52" s="2">
+        <v>19</v>
+      </c>
+      <c r="W52" s="2">
+        <v>20</v>
+      </c>
+      <c r="X52" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y52" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z52" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA52" s="2">
+        <v>24</v>
+      </c>
+      <c r="AB52" s="2">
+        <v>25</v>
+      </c>
+      <c r="AC52" s="2">
+        <v>26</v>
+      </c>
+      <c r="AD52" s="2">
+        <v>27</v>
+      </c>
+      <c r="AE52" s="2">
+        <v>28</v>
+      </c>
+      <c r="AF52" s="2">
+        <v>29</v>
+      </c>
+      <c r="AG52" s="2">
+        <v>30</v>
+      </c>
+      <c r="AH52" s="2">
+        <v>31</v>
+      </c>
+      <c r="AI52" s="2">
+        <v>32</v>
+      </c>
+      <c r="AJ52" s="2">
+        <v>33</v>
+      </c>
+      <c r="AK52" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL52" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM52" s="2">
+        <v>36</v>
+      </c>
+      <c r="AN52" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO52" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP52" s="2">
+        <v>39</v>
+      </c>
+      <c r="AQ52" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR52" s="2">
+        <v>41</v>
+      </c>
+      <c r="AS52" s="2">
+        <v>42</v>
+      </c>
+      <c r="AT52" s="2">
+        <v>43</v>
+      </c>
+      <c r="AU52" s="2">
+        <v>44</v>
+      </c>
+      <c r="AV52" s="2">
+        <v>45</v>
+      </c>
+      <c r="AW52" s="2">
+        <v>46</v>
+      </c>
+      <c r="AX52" s="2">
+        <v>47</v>
+      </c>
+      <c r="AY52" s="2">
+        <v>48</v>
+      </c>
+      <c r="AZ52" s="2">
+        <v>49</v>
+      </c>
+      <c r="BA52" s="2">
+        <v>50</v>
+      </c>
+      <c r="BB52" s="2">
+        <v>51</v>
+      </c>
+      <c r="BC52" s="2">
+        <v>52</v>
+      </c>
+      <c r="BD52" s="2">
+        <v>53</v>
+      </c>
+      <c r="BE52" s="2">
+        <v>54</v>
+      </c>
+      <c r="BF52" s="2">
+        <v>55</v>
+      </c>
+      <c r="BG52" s="2">
+        <v>56</v>
+      </c>
+      <c r="BH52" s="2">
+        <v>57</v>
+      </c>
+      <c r="BI52" s="2">
+        <v>58</v>
+      </c>
+      <c r="BJ52" s="2">
+        <v>59</v>
+      </c>
+      <c r="BK52" s="2">
+        <v>60</v>
+      </c>
+      <c r="BM52" s="67" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="67"/>
+      <c r="C53" s="67"/>
+      <c r="D53" s="67"/>
+      <c r="E53" s="67"/>
+      <c r="F53" s="67"/>
+      <c r="G53" s="67"/>
+      <c r="H53" s="67"/>
+      <c r="I53" s="67"/>
+      <c r="J53" s="67"/>
+      <c r="K53" s="67"/>
+      <c r="L53" s="67"/>
+      <c r="M53" s="67"/>
+      <c r="N53" s="67"/>
+      <c r="O53" s="67"/>
+      <c r="P53" s="67"/>
+      <c r="Q53" s="67"/>
+      <c r="R53" s="67"/>
+      <c r="S53" s="67"/>
+      <c r="T53" s="67"/>
+      <c r="U53" s="67"/>
+      <c r="V53" s="67"/>
+      <c r="W53" s="67"/>
+      <c r="X53" s="67"/>
+      <c r="Y53" s="67"/>
+      <c r="Z53" s="67"/>
+      <c r="AA53" s="67"/>
+      <c r="AB53" s="67"/>
+      <c r="AC53" s="67"/>
+      <c r="AD53" s="67"/>
+      <c r="AE53" s="67"/>
+      <c r="AF53" s="67"/>
+      <c r="AG53" s="67"/>
+      <c r="AH53" s="67"/>
+      <c r="AI53" s="67"/>
+      <c r="AJ53" s="67"/>
+      <c r="AK53" s="67"/>
+      <c r="AL53" s="67"/>
+      <c r="AM53" s="67"/>
+      <c r="AN53" s="67"/>
+      <c r="AO53" s="67"/>
+      <c r="AP53" s="67"/>
+      <c r="AQ53" s="67"/>
+      <c r="AR53" s="67"/>
+      <c r="AS53" s="67"/>
+      <c r="AT53" s="67"/>
+      <c r="AU53" s="67"/>
+      <c r="AV53" s="67"/>
+      <c r="AW53" s="67"/>
+      <c r="AX53" s="67"/>
+      <c r="AY53" s="67"/>
+      <c r="AZ53" s="67"/>
+      <c r="BA53" s="67"/>
+      <c r="BB53" s="67"/>
+      <c r="BC53" s="67"/>
+      <c r="BD53" s="67"/>
+      <c r="BE53" s="67"/>
+      <c r="BF53" s="67"/>
+      <c r="BG53" s="67"/>
+      <c r="BH53" s="67"/>
+      <c r="BI53" s="67"/>
+      <c r="BJ53" s="67"/>
+      <c r="BK53" s="67"/>
+    </row>
+    <row r="54" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2"/>
+      <c r="R54" s="2"/>
+      <c r="S54" s="2"/>
+      <c r="T54" s="2"/>
+      <c r="U54" s="2"/>
+      <c r="V54" s="2"/>
+      <c r="W54" s="2"/>
+      <c r="X54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y54" s="67"/>
+      <c r="Z54" s="67"/>
+      <c r="AA54" s="67"/>
+      <c r="AB54" s="67"/>
+      <c r="AC54" s="67"/>
+      <c r="AD54" s="67"/>
+      <c r="AE54" s="67"/>
+      <c r="AF54" s="67"/>
+      <c r="AG54" s="67"/>
+      <c r="AH54" s="67"/>
+      <c r="AI54" s="67"/>
+      <c r="AJ54" s="67"/>
+      <c r="AK54" s="67"/>
+      <c r="AL54" s="67"/>
+      <c r="AM54" s="67"/>
+      <c r="AN54" s="67"/>
+      <c r="AO54" s="67"/>
+      <c r="AP54" s="67"/>
+      <c r="AQ54" s="67"/>
+      <c r="AR54" s="67"/>
+      <c r="AS54" s="67"/>
+      <c r="AT54" s="67"/>
+      <c r="AU54" s="67"/>
+      <c r="AV54" s="67"/>
+      <c r="AW54" s="67"/>
+      <c r="AX54" s="67"/>
+      <c r="AY54" s="67"/>
+      <c r="AZ54" s="67"/>
+      <c r="BA54" s="67"/>
+      <c r="BB54" s="67"/>
+      <c r="BC54" s="67"/>
+      <c r="BD54" s="67"/>
+      <c r="BE54" s="67"/>
+      <c r="BF54" s="67"/>
+      <c r="BG54" s="67"/>
+      <c r="BH54" s="67"/>
+      <c r="BI54" s="67"/>
+      <c r="BJ54" s="67"/>
+      <c r="BK54" s="67"/>
+    </row>
+    <row r="55" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="67"/>
+      <c r="C55" s="67"/>
+      <c r="D55" s="67"/>
+      <c r="E55" s="67"/>
+      <c r="F55" s="67"/>
+      <c r="G55" s="67"/>
+      <c r="H55" s="67"/>
+      <c r="I55" s="67"/>
+      <c r="J55" s="67"/>
+      <c r="K55" s="67"/>
+      <c r="L55" s="67"/>
+      <c r="M55" s="67"/>
+      <c r="N55" s="67"/>
+      <c r="O55" s="67"/>
+      <c r="P55" s="67"/>
+      <c r="Q55" s="67"/>
+      <c r="R55" s="67"/>
+      <c r="S55" s="67"/>
+      <c r="T55" s="67"/>
+      <c r="U55" s="67"/>
+      <c r="V55" s="67"/>
+      <c r="W55" s="67"/>
+      <c r="X55" s="67"/>
+      <c r="Y55" s="67"/>
+      <c r="Z55" s="67"/>
+      <c r="AA55" s="67"/>
+      <c r="AB55" s="67"/>
+      <c r="AC55" s="67"/>
+      <c r="AD55" s="67"/>
+      <c r="AE55" s="67"/>
+      <c r="AF55" s="67"/>
+      <c r="AG55" s="67"/>
+      <c r="AH55" s="67"/>
+      <c r="AI55" s="67"/>
+      <c r="AJ55" s="67"/>
+      <c r="AK55" s="67"/>
+      <c r="AL55" s="67"/>
+      <c r="AM55" s="67"/>
+      <c r="AN55" s="67"/>
+      <c r="AO55" s="67"/>
+      <c r="AP55" s="67"/>
+      <c r="AQ55" s="67"/>
+      <c r="AR55" s="67"/>
+      <c r="AS55" s="67"/>
+      <c r="AT55" s="67"/>
+      <c r="AU55" s="67"/>
+      <c r="AV55" s="67"/>
+      <c r="AW55" s="67"/>
+      <c r="AX55" s="67"/>
+      <c r="AY55" s="67"/>
+      <c r="AZ55" s="67"/>
+      <c r="BA55" s="67"/>
+      <c r="BB55" s="67"/>
+      <c r="BC55" s="67"/>
+      <c r="BD55" s="67"/>
+      <c r="BE55" s="67"/>
+      <c r="BF55" s="67"/>
+      <c r="BG55" s="67"/>
+      <c r="BH55" s="67"/>
+      <c r="BI55" s="67"/>
+      <c r="BJ55" s="67"/>
+      <c r="BK55" s="67"/>
+    </row>
+    <row r="56" spans="2:68" x14ac:dyDescent="0.25">
+      <c r="B56" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="9"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="O56" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="P56" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q56" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="R56" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="S56" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="T56" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="U56" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="V56" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="W56" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="X56" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y56" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z56" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA56" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB56" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC56" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD56" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE56" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF56" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG56" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH56" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI56" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ56" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK56" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL56" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM56" s="6"/>
+      <c r="AN56" s="6"/>
+      <c r="AO56" s="6"/>
+      <c r="AP56" s="4"/>
+      <c r="AQ56" s="4"/>
+      <c r="AR56" s="4"/>
+      <c r="AS56" s="4"/>
+      <c r="AT56" s="4"/>
+      <c r="AU56" s="4"/>
+      <c r="AV56" s="4"/>
+      <c r="AW56" s="4"/>
+      <c r="AX56" s="4"/>
+      <c r="AY56" s="4"/>
+      <c r="AZ56" s="4"/>
+      <c r="BA56" s="4"/>
+      <c r="BB56" s="4"/>
+      <c r="BC56" s="4"/>
+      <c r="BD56" s="4"/>
+      <c r="BE56" s="4"/>
+      <c r="BF56" s="4"/>
+      <c r="BG56" s="4"/>
+      <c r="BH56" s="4"/>
+      <c r="BI56" s="4"/>
+      <c r="BJ56" s="4"/>
+      <c r="BK56" s="5"/>
+    </row>
+    <row r="57" spans="2:68" x14ac:dyDescent="0.25">
+      <c r="B57" s="23"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="L57" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="M57" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="O57" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="P57" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q57" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="R57" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="S57" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="T57" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="U57" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="V57" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="W57" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="X57" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y57" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z57" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA57" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB57" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC57" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE57" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG57" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH57" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI57" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ57" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK57" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL57" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM57" s="7"/>
+      <c r="AN57" s="12"/>
+      <c r="AO57" s="12"/>
+      <c r="AP57" s="12"/>
+      <c r="AQ57" s="12"/>
+      <c r="AR57" s="12"/>
+      <c r="AS57" s="12"/>
+      <c r="AT57" s="12"/>
+      <c r="AU57" s="12"/>
+      <c r="AV57" s="12"/>
+      <c r="AW57" s="12"/>
+      <c r="AX57" s="12"/>
+      <c r="AY57" s="12"/>
+      <c r="AZ57" s="12"/>
+      <c r="BA57" s="12"/>
+      <c r="BB57" s="12"/>
+      <c r="BC57" s="12"/>
+      <c r="BD57" s="12"/>
+      <c r="BE57" s="12"/>
+      <c r="BF57" s="12"/>
+      <c r="BG57" s="12"/>
+      <c r="BH57" s="12"/>
+      <c r="BI57" s="12"/>
+      <c r="BJ57" s="12"/>
+      <c r="BK57" s="16"/>
+    </row>
+    <row r="58" spans="2:68" x14ac:dyDescent="0.25">
+      <c r="B58" s="23"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L58" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M58" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="N58" s="7"/>
+      <c r="O58" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="P58" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="7"/>
+      <c r="R58" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="S58" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="T58" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="U58" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="V58" s="7"/>
+      <c r="W58" s="7"/>
+      <c r="X58" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y58" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z58" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA58" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB58" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC58" s="7"/>
+      <c r="AD58" s="7"/>
+      <c r="AE58" s="7"/>
+      <c r="AF58" s="7"/>
+      <c r="AG58" s="7"/>
+      <c r="AH58" s="7"/>
+      <c r="AI58" s="7"/>
+      <c r="AJ58" s="12"/>
+      <c r="AK58" s="12"/>
+      <c r="AL58" s="12"/>
+      <c r="AM58" s="12"/>
+      <c r="AN58" s="12"/>
+      <c r="AO58" s="12"/>
+      <c r="AP58" s="12"/>
+      <c r="AQ58" s="12"/>
+      <c r="AR58" s="12"/>
+      <c r="AS58" s="12"/>
+      <c r="AT58" s="12"/>
+      <c r="AU58" s="12"/>
+      <c r="AV58" s="12"/>
+      <c r="AW58" s="12"/>
+      <c r="AX58" s="12"/>
+      <c r="AY58" s="12"/>
+      <c r="AZ58" s="12"/>
+      <c r="BA58" s="12"/>
+      <c r="BB58" s="12"/>
+      <c r="BC58" s="12"/>
+      <c r="BD58" s="12"/>
+      <c r="BE58" s="12"/>
+      <c r="BF58" s="12"/>
+      <c r="BG58" s="12"/>
+      <c r="BH58" s="12"/>
+      <c r="BI58" s="12"/>
+      <c r="BJ58" s="12"/>
+      <c r="BK58" s="16"/>
+    </row>
+    <row r="59" spans="2:68" x14ac:dyDescent="0.25">
+      <c r="B59" s="23"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7"/>
+      <c r="K59" s="7"/>
+      <c r="L59" s="7"/>
+      <c r="M59" s="7"/>
+      <c r="N59" s="7"/>
+      <c r="O59" s="7"/>
+      <c r="P59" s="7"/>
+      <c r="Q59" s="7"/>
+      <c r="R59" s="7"/>
+      <c r="S59" s="7"/>
+      <c r="T59" s="7"/>
+      <c r="U59" s="7"/>
+      <c r="V59" s="7"/>
+      <c r="W59" s="7"/>
+      <c r="X59" s="7"/>
+      <c r="Y59" s="7"/>
+      <c r="Z59" s="7"/>
+      <c r="AA59" s="7"/>
+      <c r="AB59" s="7"/>
+      <c r="AC59" s="7"/>
+      <c r="AD59" s="7"/>
+      <c r="AE59" s="7"/>
+      <c r="AF59" s="7"/>
+      <c r="AG59" s="7"/>
+      <c r="AH59" s="7"/>
+      <c r="AI59" s="7"/>
+      <c r="AJ59" s="12"/>
+      <c r="AK59" s="12"/>
+      <c r="AL59" s="12"/>
+      <c r="AM59" s="12"/>
+      <c r="AN59" s="12"/>
+      <c r="AO59" s="12"/>
+      <c r="AP59" s="12"/>
+      <c r="AQ59" s="12"/>
+      <c r="AR59" s="12"/>
+      <c r="AS59" s="12"/>
+      <c r="AT59" s="12"/>
+      <c r="AU59" s="12"/>
+      <c r="AV59" s="12"/>
+      <c r="AW59" s="12"/>
+      <c r="AX59" s="12"/>
+      <c r="AY59" s="12"/>
+      <c r="AZ59" s="12"/>
+      <c r="BA59" s="12"/>
+      <c r="BB59" s="12"/>
+      <c r="BC59" s="12"/>
+      <c r="BD59" s="12"/>
+      <c r="BE59" s="12"/>
+      <c r="BF59" s="12"/>
+      <c r="BG59" s="12"/>
+      <c r="BH59" s="12"/>
+      <c r="BI59" s="12"/>
+      <c r="BJ59" s="12"/>
+      <c r="BK59" s="16"/>
+    </row>
+    <row r="60" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="24"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="8"/>
+      <c r="J60" s="8"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="8"/>
+      <c r="M60" s="8"/>
+      <c r="N60" s="8"/>
+      <c r="O60" s="8"/>
+      <c r="P60" s="8"/>
+      <c r="Q60" s="8"/>
+      <c r="R60" s="8"/>
+      <c r="S60" s="8"/>
+      <c r="T60" s="8"/>
+      <c r="U60" s="8"/>
+      <c r="V60" s="8"/>
+      <c r="W60" s="8"/>
+      <c r="X60" s="8"/>
+      <c r="Y60" s="8"/>
+      <c r="Z60" s="8"/>
+      <c r="AA60" s="8"/>
+      <c r="AB60" s="8"/>
+      <c r="AC60" s="8"/>
+      <c r="AD60" s="8"/>
+      <c r="AE60" s="8"/>
+      <c r="AF60" s="8"/>
+      <c r="AG60" s="8"/>
+      <c r="AH60" s="8"/>
+      <c r="AI60" s="8"/>
+      <c r="AJ60" s="17"/>
+      <c r="AK60" s="17"/>
+      <c r="AL60" s="17"/>
+      <c r="AM60" s="17"/>
+      <c r="AN60" s="17"/>
+      <c r="AO60" s="17"/>
+      <c r="AP60" s="17"/>
+      <c r="AQ60" s="17"/>
+      <c r="AR60" s="17"/>
+      <c r="AS60" s="17"/>
+      <c r="AT60" s="17"/>
+      <c r="AU60" s="17"/>
+      <c r="AV60" s="17"/>
+      <c r="AW60" s="17"/>
+      <c r="AX60" s="17"/>
+      <c r="AY60" s="17"/>
+      <c r="AZ60" s="17"/>
+      <c r="BA60" s="17"/>
+      <c r="BB60" s="17"/>
+      <c r="BC60" s="17"/>
+      <c r="BD60" s="17"/>
+      <c r="BE60" s="17"/>
+      <c r="BF60" s="17"/>
+      <c r="BG60" s="17"/>
+      <c r="BH60" s="17"/>
+      <c r="BI60" s="17"/>
+      <c r="BJ60" s="17"/>
+      <c r="BK60" s="18"/>
+    </row>
+    <row r="61" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="67"/>
+      <c r="C61" s="67"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="67"/>
+      <c r="J61" s="67"/>
+      <c r="K61" s="67"/>
+      <c r="L61" s="67"/>
+      <c r="M61" s="67"/>
+      <c r="N61" s="67"/>
+      <c r="O61" s="67"/>
+      <c r="P61" s="67"/>
+      <c r="Q61" s="67"/>
+      <c r="R61" s="67"/>
+      <c r="S61" s="67"/>
+      <c r="T61" s="67"/>
+      <c r="U61" s="67"/>
+      <c r="V61" s="67"/>
+      <c r="W61" s="67"/>
+      <c r="X61" s="67"/>
+      <c r="Y61" s="67"/>
+      <c r="Z61" s="67"/>
+      <c r="AA61" s="67"/>
+      <c r="AB61" s="67"/>
+      <c r="AC61" s="67"/>
+      <c r="AD61" s="67"/>
+      <c r="AE61" s="67"/>
+      <c r="AF61" s="67"/>
+      <c r="AG61" s="67"/>
+      <c r="AH61" s="67"/>
+      <c r="AI61" s="67"/>
+      <c r="AJ61" s="67"/>
+      <c r="AK61" s="67"/>
+      <c r="AL61" s="67"/>
+      <c r="AM61" s="67"/>
+      <c r="AN61" s="67"/>
+      <c r="AO61" s="67"/>
+      <c r="AP61" s="67"/>
+      <c r="AQ61" s="67"/>
+      <c r="AR61" s="67"/>
+      <c r="AS61" s="67"/>
+      <c r="AT61" s="67"/>
+      <c r="AU61" s="67"/>
+      <c r="AV61" s="67"/>
+      <c r="AW61" s="67"/>
+      <c r="AX61" s="67"/>
+      <c r="AY61" s="67"/>
+      <c r="AZ61" s="67"/>
+      <c r="BA61" s="67"/>
+      <c r="BB61" s="67"/>
+      <c r="BC61" s="67"/>
+      <c r="BD61" s="67"/>
+      <c r="BE61" s="67"/>
+      <c r="BF61" s="67"/>
+      <c r="BG61" s="67"/>
+      <c r="BH61" s="67"/>
+      <c r="BI61" s="67"/>
+      <c r="BJ61" s="67"/>
+      <c r="BK61" s="67"/>
+    </row>
+    <row r="62" spans="2:68" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="63"/>
+      <c r="D62" s="63"/>
+      <c r="E62" s="63"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="63"/>
+      <c r="H62" s="63"/>
+      <c r="I62" s="63"/>
+      <c r="J62" s="63"/>
+      <c r="K62" s="63"/>
+      <c r="L62" s="63"/>
+      <c r="M62" s="63"/>
+      <c r="N62" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="O62" s="63"/>
+      <c r="P62" s="63"/>
+      <c r="Q62" s="63"/>
+      <c r="R62" s="63"/>
+      <c r="S62" s="63"/>
+      <c r="T62" s="63"/>
+      <c r="U62" s="63"/>
+      <c r="V62" s="63"/>
+      <c r="W62" s="63"/>
+      <c r="X62" s="63"/>
+      <c r="Y62" s="63"/>
+      <c r="Z62" s="63"/>
+      <c r="AA62" s="63"/>
+      <c r="AB62" s="63"/>
+      <c r="AC62" s="63"/>
+      <c r="AD62" s="63"/>
+      <c r="AE62" s="63"/>
+      <c r="AF62" s="63"/>
+      <c r="AG62" s="63"/>
+      <c r="AH62" s="63"/>
+      <c r="AI62" s="63"/>
+      <c r="AJ62" s="63"/>
+      <c r="AK62" s="63"/>
+      <c r="AL62" s="63"/>
+      <c r="AM62" s="63"/>
+      <c r="AN62" s="63"/>
+      <c r="AO62" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP62" s="63"/>
+      <c r="AQ62" s="63"/>
+      <c r="AR62" s="63"/>
+      <c r="AS62" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="AT62" s="63"/>
+      <c r="AU62" s="63"/>
+      <c r="AV62" s="63"/>
+      <c r="AW62" s="63"/>
+      <c r="AX62" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY62" s="63"/>
+      <c r="AZ62" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="BA62" s="63"/>
+      <c r="BB62" s="63"/>
+      <c r="BC62" s="63"/>
+      <c r="BD62" s="63"/>
+      <c r="BE62" s="63"/>
+      <c r="BF62" s="63"/>
+      <c r="BG62" s="63"/>
+      <c r="BH62" s="63"/>
+      <c r="BI62" s="63"/>
+      <c r="BJ62" s="63"/>
+      <c r="BK62" s="68"/>
+    </row>
+    <row r="66" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="C69" s="29"/>
+      <c r="D69" s="29"/>
+      <c r="E69" s="29"/>
+      <c r="F69" s="29"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="29"/>
+      <c r="I69" s="29"/>
+      <c r="J69" s="29"/>
+      <c r="K69" s="29"/>
+      <c r="L69" s="29"/>
+      <c r="M69" s="29"/>
+      <c r="N69" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="O69" s="77"/>
+      <c r="P69" s="77"/>
+      <c r="Q69" s="78"/>
+      <c r="R69" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="S69" s="29"/>
+      <c r="T69" s="29"/>
+      <c r="U69" s="29"/>
+      <c r="V69" s="29"/>
+      <c r="W69" s="29"/>
+      <c r="X69" s="29"/>
+      <c r="Y69" s="29"/>
+      <c r="Z69" s="29"/>
+      <c r="AA69" s="29"/>
+      <c r="AB69" s="29"/>
+      <c r="AC69" s="29"/>
+      <c r="AD69" s="29"/>
+      <c r="AE69" s="29"/>
+      <c r="AF69" s="29"/>
+      <c r="AG69" s="29"/>
+      <c r="AH69" s="29"/>
+      <c r="AI69" s="29"/>
+      <c r="AJ69" s="29"/>
+      <c r="AK69" s="29"/>
+      <c r="AL69" s="29"/>
+      <c r="AM69" s="29"/>
+      <c r="AN69" s="29"/>
+      <c r="AO69" s="29"/>
+      <c r="AP69" s="29"/>
+      <c r="AQ69" s="29"/>
+      <c r="AR69" s="29"/>
+      <c r="AS69" s="29"/>
+      <c r="AT69" s="29"/>
+      <c r="AU69" s="29"/>
+      <c r="AV69" s="29"/>
+      <c r="AW69" s="29"/>
+      <c r="AX69" s="29"/>
+      <c r="AY69" s="29"/>
+      <c r="AZ69" s="29"/>
+      <c r="BA69" s="29"/>
+      <c r="BB69" s="29"/>
+      <c r="BC69" s="29"/>
+      <c r="BD69" s="29"/>
+      <c r="BE69" s="29"/>
+      <c r="BF69" s="29"/>
+      <c r="BG69" s="29"/>
+      <c r="BH69" s="29"/>
+      <c r="BI69" s="29"/>
+      <c r="BJ69" s="29"/>
+      <c r="BK69" s="30"/>
+    </row>
+    <row r="70" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
+      <c r="J70" s="31"/>
+      <c r="K70" s="31"/>
+      <c r="L70" s="31"/>
+      <c r="M70" s="31"/>
+      <c r="N70" s="31"/>
+      <c r="O70" s="31"/>
+      <c r="P70" s="31"/>
+      <c r="Q70" s="31"/>
+      <c r="R70" s="31"/>
+      <c r="S70" s="31"/>
+      <c r="T70" s="31"/>
+      <c r="U70" s="31"/>
+      <c r="V70" s="31"/>
+      <c r="W70" s="31"/>
+      <c r="X70" s="31"/>
+      <c r="Y70" s="31"/>
+      <c r="Z70" s="79" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA70" s="80"/>
+      <c r="AB70" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC70" s="31"/>
+      <c r="AD70" s="31"/>
+      <c r="AE70" s="31"/>
+      <c r="AF70" s="31"/>
+      <c r="AG70" s="31"/>
+      <c r="AH70" s="31"/>
+      <c r="AI70" s="31"/>
+      <c r="AJ70" s="31"/>
+      <c r="AK70" s="31"/>
+      <c r="AL70" s="31"/>
+      <c r="AM70" s="81" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN70" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO70" s="31"/>
+      <c r="AP70" s="31"/>
+      <c r="AQ70" s="31"/>
+      <c r="AR70" s="31"/>
+      <c r="AS70" s="31"/>
+      <c r="AT70" s="31"/>
+      <c r="AU70" s="31"/>
+      <c r="AV70" s="31"/>
+      <c r="AW70" s="31"/>
+      <c r="AX70" s="31"/>
+      <c r="AY70" s="31"/>
+      <c r="AZ70" s="31"/>
+      <c r="BA70" s="31"/>
+      <c r="BB70" s="31"/>
+      <c r="BC70" s="31"/>
+      <c r="BD70" s="31"/>
+      <c r="BE70" s="31"/>
+      <c r="BF70" s="31"/>
+      <c r="BG70" s="31"/>
+      <c r="BH70" s="31"/>
+      <c r="BI70" s="31"/>
+      <c r="BJ70" s="31"/>
+      <c r="BK70" s="32"/>
+    </row>
+    <row r="71" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="C71" s="31"/>
+      <c r="D71" s="31"/>
+      <c r="E71" s="31"/>
+      <c r="F71" s="31"/>
+      <c r="G71" s="31"/>
+      <c r="H71" s="31"/>
+      <c r="I71" s="31"/>
+      <c r="J71" s="31"/>
+      <c r="K71" s="31"/>
+      <c r="L71" s="31"/>
+      <c r="M71" s="31"/>
+      <c r="N71" s="31"/>
+      <c r="O71" s="31"/>
+      <c r="P71" s="31"/>
+      <c r="Q71" s="31"/>
+      <c r="R71" s="82" t="s">
+        <v>2</v>
+      </c>
+      <c r="S71" s="83"/>
+      <c r="T71" s="84"/>
+      <c r="U71" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="V71" s="31"/>
+      <c r="W71" s="31"/>
+      <c r="X71" s="31"/>
+      <c r="Y71" s="31"/>
+      <c r="Z71" s="31"/>
+      <c r="AA71" s="31"/>
+      <c r="AB71" s="31"/>
+      <c r="AC71" s="31"/>
+      <c r="AD71" s="31"/>
+      <c r="AE71" s="31"/>
+      <c r="AF71" s="31"/>
+      <c r="AG71" s="82" t="s">
+        <v>2</v>
+      </c>
+      <c r="AH71" s="84"/>
+      <c r="AI71" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ71" s="31"/>
+      <c r="AK71" s="31"/>
+      <c r="AL71" s="31"/>
+      <c r="AM71" s="31"/>
+      <c r="AN71" s="82" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO71" s="83"/>
+      <c r="AP71" s="83"/>
+      <c r="AQ71" s="84"/>
+      <c r="AR71" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS71" s="31"/>
+      <c r="AT71" s="31"/>
+      <c r="AU71" s="31"/>
+      <c r="AV71" s="31"/>
+      <c r="AW71" s="31"/>
+      <c r="AX71" s="31"/>
+      <c r="AY71" s="31"/>
+      <c r="AZ71" s="31"/>
+      <c r="BA71" s="31"/>
+      <c r="BB71" s="31"/>
+      <c r="BC71" s="31"/>
+      <c r="BD71" s="31"/>
+      <c r="BE71" s="31"/>
+      <c r="BF71" s="31"/>
+      <c r="BG71" s="31"/>
+      <c r="BH71" s="31"/>
+      <c r="BI71" s="31"/>
+      <c r="BJ71" s="31"/>
+      <c r="BK71" s="32"/>
+    </row>
+    <row r="72" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72" s="31"/>
+      <c r="D72" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="74"/>
+      <c r="F72" s="74"/>
+      <c r="G72" s="74"/>
+      <c r="H72" s="75"/>
+      <c r="I72" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" s="31"/>
+      <c r="K72" s="31"/>
+      <c r="L72" s="31"/>
+      <c r="M72" s="31"/>
+      <c r="N72" s="31"/>
+      <c r="O72" s="31"/>
+      <c r="P72" s="31"/>
+      <c r="Q72" s="31"/>
+      <c r="R72" s="31"/>
+      <c r="S72" s="31"/>
+      <c r="T72" s="31"/>
+      <c r="U72" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="74"/>
+      <c r="W72" s="74"/>
+      <c r="X72" s="74"/>
+      <c r="Y72" s="75"/>
+      <c r="Z72" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA72" s="31"/>
+      <c r="AB72" s="31"/>
+      <c r="AC72" s="31"/>
+      <c r="AD72" s="31"/>
+      <c r="AE72" s="31"/>
+      <c r="AF72" s="31"/>
+      <c r="AG72" s="31"/>
+      <c r="AH72" s="31"/>
+      <c r="AI72" s="31"/>
+      <c r="AJ72" s="31"/>
+      <c r="AK72" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL72" s="75"/>
+      <c r="AM72" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN72" s="31"/>
+      <c r="AO72" s="31"/>
+      <c r="AP72" s="31"/>
+      <c r="AQ72" s="31"/>
+      <c r="AR72" s="31"/>
+      <c r="AS72" s="31"/>
+      <c r="AT72" s="31"/>
+      <c r="AU72" s="31"/>
+      <c r="AV72" s="31"/>
+      <c r="AW72" s="31"/>
+      <c r="AX72" s="31"/>
+      <c r="AY72" s="31"/>
+      <c r="AZ72" s="31"/>
+      <c r="BA72" s="31"/>
+      <c r="BB72" s="31"/>
+      <c r="BC72" s="31"/>
+      <c r="BD72" s="31"/>
+      <c r="BE72" s="31"/>
+      <c r="BF72" s="31"/>
+      <c r="BG72" s="31"/>
+      <c r="BH72" s="31"/>
+      <c r="BI72" s="31"/>
+      <c r="BJ72" s="31"/>
+      <c r="BK72" s="32"/>
+    </row>
+    <row r="73" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="C73" s="31"/>
+      <c r="D73" s="31"/>
+      <c r="E73" s="31"/>
+      <c r="F73" s="31"/>
+      <c r="G73" s="31"/>
+      <c r="H73" s="31"/>
+      <c r="I73" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="J73" s="71"/>
+      <c r="K73" s="71"/>
+      <c r="L73" s="71"/>
+      <c r="M73" s="72"/>
+      <c r="N73" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="O73" s="31"/>
+      <c r="P73" s="31"/>
+      <c r="Q73" s="31"/>
+      <c r="R73" s="31"/>
+      <c r="S73" s="31"/>
+      <c r="T73" s="31"/>
+      <c r="U73" s="31"/>
+      <c r="V73" s="31"/>
+      <c r="W73" s="31"/>
+      <c r="X73" s="31"/>
+      <c r="Y73" s="31"/>
+      <c r="Z73" s="31"/>
+      <c r="AA73" s="31"/>
+      <c r="AB73" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC73" s="71"/>
+      <c r="AD73" s="71"/>
+      <c r="AE73" s="71"/>
+      <c r="AF73" s="72"/>
+      <c r="AG73" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH73" s="31"/>
+      <c r="AI73" s="31"/>
+      <c r="AJ73" s="31"/>
+      <c r="AK73" s="31"/>
+      <c r="AL73" s="31"/>
+      <c r="AM73" s="31"/>
+      <c r="AN73" s="31"/>
+      <c r="AO73" s="31"/>
+      <c r="AP73" s="31"/>
+      <c r="AQ73" s="31"/>
+      <c r="AR73" s="31"/>
+      <c r="AS73" s="31"/>
+      <c r="AT73" s="31"/>
+      <c r="AU73" s="31"/>
+      <c r="AV73" s="31"/>
+      <c r="AW73" s="31"/>
+      <c r="AX73" s="31"/>
+      <c r="AY73" s="31"/>
+      <c r="AZ73" s="31"/>
+      <c r="BA73" s="31"/>
+      <c r="BB73" s="31"/>
+      <c r="BC73" s="31"/>
+      <c r="BD73" s="31"/>
+      <c r="BE73" s="31"/>
+      <c r="BF73" s="31"/>
+      <c r="BG73" s="31"/>
+      <c r="BH73" s="31"/>
+      <c r="BI73" s="31"/>
+      <c r="BJ73" s="31"/>
+      <c r="BK73" s="32"/>
+    </row>
+    <row r="74" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="31"/>
+      <c r="D74" s="31"/>
+      <c r="E74" s="31"/>
+      <c r="F74" s="31"/>
+      <c r="G74" s="31"/>
+      <c r="H74" s="31"/>
+      <c r="I74" s="31"/>
+      <c r="J74" s="31"/>
+      <c r="K74" s="31"/>
+      <c r="L74" s="31"/>
+      <c r="M74" s="31"/>
+      <c r="N74" s="31"/>
+      <c r="O74" s="31"/>
+      <c r="P74" s="31"/>
+      <c r="Q74" s="31"/>
+      <c r="R74" s="31"/>
+      <c r="S74" s="31"/>
+      <c r="T74" s="31"/>
+      <c r="U74" s="31"/>
+      <c r="V74" s="31"/>
+      <c r="W74" s="31"/>
+      <c r="X74" s="31"/>
+      <c r="Y74" s="31"/>
+      <c r="Z74" s="31"/>
+      <c r="AA74" s="31"/>
+      <c r="AB74" s="31"/>
+      <c r="AC74" s="31"/>
+      <c r="AD74" s="31"/>
+      <c r="AE74" s="31"/>
+      <c r="AF74" s="31"/>
+      <c r="AG74" s="31"/>
+      <c r="AH74" s="31"/>
+      <c r="AI74" s="64" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ74" s="66"/>
+      <c r="AK74" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL74" s="31"/>
+      <c r="AM74" s="31"/>
+      <c r="AN74" s="31"/>
+      <c r="AO74" s="31"/>
+      <c r="AP74" s="31"/>
+      <c r="AQ74" s="31"/>
+      <c r="AR74" s="64" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS74" s="65"/>
+      <c r="AT74" s="65"/>
+      <c r="AU74" s="65"/>
+      <c r="AV74" s="66"/>
+      <c r="AW74" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX74" s="69" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY74" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="AZ74" s="64" t="s">
+        <v>5</v>
+      </c>
+      <c r="BA74" s="65"/>
+      <c r="BB74" s="65"/>
+      <c r="BC74" s="66"/>
+      <c r="BD74" s="31"/>
+      <c r="BE74" s="31"/>
+      <c r="BF74" s="31"/>
+      <c r="BG74" s="31"/>
+      <c r="BH74" s="31"/>
+      <c r="BI74" s="31"/>
+      <c r="BJ74" s="31"/>
+      <c r="BK74" s="32"/>
+    </row>
+    <row r="75" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="2"/>
+      <c r="C75" s="2">
+        <v>0</v>
+      </c>
+      <c r="D75" s="2">
+        <v>1</v>
+      </c>
+      <c r="E75" s="2">
+        <v>2</v>
+      </c>
+      <c r="F75" s="2">
+        <v>3</v>
+      </c>
+      <c r="G75" s="2">
+        <v>4</v>
+      </c>
+      <c r="H75" s="2">
+        <v>5</v>
+      </c>
+      <c r="I75" s="2">
+        <v>6</v>
+      </c>
+      <c r="J75" s="2">
+        <v>7</v>
+      </c>
+      <c r="K75" s="2">
+        <v>8</v>
+      </c>
+      <c r="L75" s="2">
+        <v>9</v>
+      </c>
+      <c r="M75" s="2">
+        <v>10</v>
+      </c>
+      <c r="N75" s="2">
+        <v>11</v>
+      </c>
+      <c r="O75" s="2">
+        <v>12</v>
+      </c>
+      <c r="P75" s="2">
+        <v>13</v>
+      </c>
+      <c r="Q75" s="2">
+        <v>14</v>
+      </c>
+      <c r="R75" s="2">
+        <v>15</v>
+      </c>
+      <c r="S75" s="2">
+        <v>16</v>
+      </c>
+      <c r="T75" s="2">
+        <v>17</v>
+      </c>
+      <c r="U75" s="2">
+        <v>18</v>
+      </c>
+      <c r="V75" s="2">
+        <v>19</v>
+      </c>
+      <c r="W75" s="2">
+        <v>20</v>
+      </c>
+      <c r="X75" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y75" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z75" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA75" s="2">
+        <v>24</v>
+      </c>
+      <c r="AB75" s="2">
+        <v>25</v>
+      </c>
+      <c r="AC75" s="2">
+        <v>26</v>
+      </c>
+      <c r="AD75" s="2">
+        <v>27</v>
+      </c>
+      <c r="AE75" s="2">
+        <v>28</v>
+      </c>
+      <c r="AF75" s="2">
+        <v>29</v>
+      </c>
+      <c r="AG75" s="2">
+        <v>30</v>
+      </c>
+      <c r="AH75" s="2">
+        <v>31</v>
+      </c>
+      <c r="AI75" s="2">
+        <v>32</v>
+      </c>
+      <c r="AJ75" s="2">
+        <v>33</v>
+      </c>
+      <c r="AK75" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL75" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM75" s="2">
+        <v>36</v>
+      </c>
+      <c r="AN75" s="2">
+        <v>37</v>
+      </c>
+      <c r="AO75" s="2">
+        <v>38</v>
+      </c>
+      <c r="AP75" s="2">
+        <v>39</v>
+      </c>
+      <c r="AQ75" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR75" s="2">
+        <v>41</v>
+      </c>
+      <c r="AS75" s="2">
+        <v>42</v>
+      </c>
+      <c r="AT75" s="2">
+        <v>43</v>
+      </c>
+      <c r="AU75" s="2">
+        <v>44</v>
+      </c>
+      <c r="AV75" s="2">
+        <v>45</v>
+      </c>
+      <c r="AW75" s="2">
+        <v>46</v>
+      </c>
+      <c r="AX75" s="2">
+        <v>47</v>
+      </c>
+      <c r="AY75" s="2">
+        <v>48</v>
+      </c>
+      <c r="AZ75" s="2">
+        <v>49</v>
+      </c>
+      <c r="BA75" s="2">
+        <v>50</v>
+      </c>
+      <c r="BB75" s="2">
+        <v>51</v>
+      </c>
+      <c r="BC75" s="2">
+        <v>52</v>
+      </c>
+      <c r="BD75" s="2">
+        <v>53</v>
+      </c>
+      <c r="BE75" s="2">
+        <v>54</v>
+      </c>
+      <c r="BF75" s="2">
+        <v>55</v>
+      </c>
+      <c r="BG75" s="2">
+        <v>56</v>
+      </c>
+      <c r="BH75" s="2">
+        <v>57</v>
+      </c>
+      <c r="BI75" s="2">
+        <v>58</v>
+      </c>
+      <c r="BJ75" s="2">
+        <v>59</v>
+      </c>
+      <c r="BK75" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+      <c r="N77" s="1"/>
+      <c r="O77" s="1"/>
+      <c r="P77" s="1"/>
+      <c r="Q77" s="1"/>
+      <c r="R77" s="1"/>
+      <c r="S77" s="1"/>
+      <c r="T77" s="1"/>
+      <c r="U77" s="1"/>
+      <c r="V77" s="1"/>
+      <c r="W77" s="1"/>
+      <c r="X77" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B79" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" s="9"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J79" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="K79" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="L79" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="M79" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N79" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O79" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P79" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q79" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R79" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="S79" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="T79" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="U79" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="V79" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="W79" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="X79" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y79" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z79" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA79" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB79" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC79" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD79" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE79" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF79" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG79" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH79" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI79" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ79" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK79" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL79" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM79" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN79" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO79" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP79" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ79" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AR79" s="4"/>
+      <c r="AS79" s="4"/>
+      <c r="AT79" s="4"/>
+      <c r="AU79" s="4"/>
+      <c r="AV79" s="4"/>
+      <c r="AW79" s="4"/>
+      <c r="AX79" s="4"/>
+      <c r="AY79" s="4"/>
+      <c r="AZ79" s="4"/>
+      <c r="BA79" s="4"/>
+      <c r="BB79" s="4"/>
+      <c r="BC79" s="4"/>
+      <c r="BD79" s="4"/>
+      <c r="BE79" s="4"/>
+      <c r="BF79" s="4"/>
+      <c r="BG79" s="4"/>
+      <c r="BH79" s="4"/>
+      <c r="BI79" s="4"/>
+      <c r="BJ79" s="4"/>
+      <c r="BK79" s="5"/>
+    </row>
+    <row r="80" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B80" s="23"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="7"/>
+      <c r="G80" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H80" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I80" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="J80" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="K80" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="L80" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M80" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="N80" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="S80" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="T80" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="U80" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="V80" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="W80" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="X80" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y80" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z80" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA80" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB80" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC80" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD80" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE80" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF80" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG80" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH80" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI80" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ80" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK80" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL80" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM80" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN80" s="12"/>
+      <c r="AO80" s="12"/>
+      <c r="AP80" s="12"/>
+      <c r="AQ80" s="12"/>
+      <c r="AR80" s="12"/>
+      <c r="AS80" s="12"/>
+      <c r="AT80" s="12"/>
+      <c r="AU80" s="12"/>
+      <c r="AV80" s="12"/>
+      <c r="AW80" s="12"/>
+      <c r="AX80" s="12"/>
+      <c r="AY80" s="12"/>
+      <c r="AZ80" s="12"/>
+      <c r="BA80" s="12"/>
+      <c r="BB80" s="12"/>
+      <c r="BC80" s="12"/>
+      <c r="BD80" s="12"/>
+      <c r="BE80" s="12"/>
+      <c r="BF80" s="12"/>
+      <c r="BG80" s="12"/>
+      <c r="BH80" s="12"/>
+      <c r="BI80" s="12"/>
+      <c r="BJ80" s="12"/>
+      <c r="BK80" s="16"/>
+    </row>
+    <row r="81" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B81" s="23"/>
+      <c r="C81" s="10"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="K81" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="L81" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="O81" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="P81" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q81" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="R81" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="T81" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="U81" s="7"/>
+      <c r="V81" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="W81" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="X81" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y81" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z81" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA81" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB81" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC81" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD81" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE81" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF81" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG81" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH81" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI81" s="7"/>
+      <c r="AJ81" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK81" s="12"/>
+      <c r="AL81" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM81" s="12"/>
+      <c r="AN81" s="12"/>
+      <c r="AO81" s="12"/>
+      <c r="AP81" s="12"/>
+      <c r="AQ81" s="12"/>
+      <c r="AR81" s="12"/>
+      <c r="AS81" s="12"/>
+      <c r="AT81" s="12"/>
+      <c r="AU81" s="12"/>
+      <c r="AV81" s="12"/>
+      <c r="AW81" s="12"/>
+      <c r="AX81" s="12"/>
+      <c r="AY81" s="12"/>
+      <c r="AZ81" s="12"/>
+      <c r="BA81" s="12"/>
+      <c r="BB81" s="12"/>
+      <c r="BC81" s="12"/>
+      <c r="BD81" s="12"/>
+      <c r="BE81" s="12"/>
+      <c r="BF81" s="12"/>
+      <c r="BG81" s="12"/>
+      <c r="BH81" s="12"/>
+      <c r="BI81" s="12"/>
+      <c r="BJ81" s="12"/>
+      <c r="BK81" s="16"/>
+    </row>
+    <row r="82" spans="2:63" x14ac:dyDescent="0.25">
+      <c r="B82" s="23"/>
+      <c r="C82" s="10"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="7"/>
+      <c r="G82" s="7"/>
+      <c r="H82" s="7"/>
+      <c r="I82" s="7"/>
+      <c r="J82" s="7"/>
+      <c r="K82" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="L82" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="M82" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="N82" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="O82" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="P82" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q82" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="R82" s="7"/>
+      <c r="S82" s="7"/>
+      <c r="T82" s="7"/>
+      <c r="U82" s="7"/>
+      <c r="V82" s="7"/>
+      <c r="W82" s="7"/>
+      <c r="X82" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y82" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z82" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA82" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB82" s="7"/>
+      <c r="AC82" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD82" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE82" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF82" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG82" s="7"/>
+      <c r="AH82" s="7"/>
+      <c r="AI82" s="7"/>
+      <c r="AJ82" s="12"/>
+      <c r="AK82" s="12"/>
+      <c r="AL82" s="12"/>
+      <c r="AM82" s="12"/>
+      <c r="AN82" s="12"/>
+      <c r="AO82" s="12"/>
+      <c r="AP82" s="12"/>
+      <c r="AQ82" s="12"/>
+      <c r="AR82" s="12"/>
+      <c r="AS82" s="12"/>
+      <c r="AT82" s="12"/>
+      <c r="AU82" s="12"/>
+      <c r="AV82" s="12"/>
+      <c r="AW82" s="12"/>
+      <c r="AX82" s="12"/>
+      <c r="AY82" s="12"/>
+      <c r="AZ82" s="12"/>
+      <c r="BA82" s="12"/>
+      <c r="BB82" s="12"/>
+      <c r="BC82" s="12"/>
+      <c r="BD82" s="12"/>
+      <c r="BE82" s="12"/>
+      <c r="BF82" s="12"/>
+      <c r="BG82" s="12"/>
+      <c r="BH82" s="12"/>
+      <c r="BI82" s="12"/>
+      <c r="BJ82" s="12"/>
+      <c r="BK82" s="16"/>
+    </row>
+    <row r="83" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="24"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="8"/>
+      <c r="J83" s="8"/>
+      <c r="K83" s="8"/>
+      <c r="L83" s="8"/>
+      <c r="M83" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="8"/>
+      <c r="O83" s="8"/>
+      <c r="P83" s="8"/>
+      <c r="Q83" s="8"/>
+      <c r="R83" s="8"/>
+      <c r="S83" s="8"/>
+      <c r="T83" s="8"/>
+      <c r="U83" s="8"/>
+      <c r="V83" s="8"/>
+      <c r="W83" s="8"/>
+      <c r="X83" s="8"/>
+      <c r="Y83" s="8"/>
+      <c r="Z83" s="8"/>
+      <c r="AA83" s="8"/>
+      <c r="AB83" s="8"/>
+      <c r="AC83" s="8"/>
+      <c r="AD83" s="8"/>
+      <c r="AE83" s="8"/>
+      <c r="AF83" s="8"/>
+      <c r="AG83" s="8"/>
+      <c r="AH83" s="8"/>
+      <c r="AI83" s="8"/>
+      <c r="AJ83" s="17"/>
+      <c r="AK83" s="17"/>
+      <c r="AL83" s="17"/>
+      <c r="AM83" s="17"/>
+      <c r="AN83" s="17"/>
+      <c r="AO83" s="17"/>
+      <c r="AP83" s="17"/>
+      <c r="AQ83" s="17"/>
+      <c r="AR83" s="17"/>
+      <c r="AS83" s="17"/>
+      <c r="AT83" s="17"/>
+      <c r="AU83" s="17"/>
+      <c r="AV83" s="17"/>
+      <c r="AW83" s="17"/>
+      <c r="AX83" s="17"/>
+      <c r="AY83" s="17"/>
+      <c r="AZ83" s="17"/>
+      <c r="BA83" s="17"/>
+      <c r="BB83" s="17"/>
+      <c r="BC83" s="17"/>
+      <c r="BD83" s="17"/>
+      <c r="BE83" s="17"/>
+      <c r="BF83" s="17"/>
+      <c r="BG83" s="17"/>
+      <c r="BH83" s="17"/>
+      <c r="BI83" s="17"/>
+      <c r="BJ83" s="17"/>
+      <c r="BK83" s="18"/>
+    </row>
+    <row r="84" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="85" spans="2:63" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B85" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" s="14"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="14"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="14"/>
+      <c r="K85" s="14"/>
+      <c r="L85" s="14"/>
+      <c r="M85" s="14"/>
+      <c r="N85" s="14"/>
+      <c r="O85" s="14"/>
+      <c r="P85" s="14"/>
+      <c r="Q85" s="14"/>
+      <c r="R85" s="14"/>
+      <c r="S85" s="14"/>
+      <c r="T85" s="14"/>
+      <c r="U85" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="V85" s="14"/>
+      <c r="W85" s="14"/>
+      <c r="X85" s="14"/>
+      <c r="Y85" s="14"/>
+      <c r="Z85" s="14"/>
+      <c r="AA85" s="14"/>
+      <c r="AB85" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC85" s="14"/>
+      <c r="AD85" s="14"/>
+      <c r="AE85" s="14"/>
+      <c r="AF85" s="14"/>
+      <c r="AG85" s="14"/>
+      <c r="AH85" s="14"/>
+      <c r="AI85" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ85" s="14"/>
+      <c r="AK85" s="14"/>
+      <c r="AL85" s="14"/>
+      <c r="AM85" s="14"/>
+      <c r="AN85" s="14"/>
+      <c r="AO85" s="14"/>
+      <c r="AP85" s="14"/>
+      <c r="AQ85" s="14"/>
+      <c r="AR85" s="14"/>
+      <c r="AS85" s="14"/>
+      <c r="AT85" s="14"/>
+      <c r="AU85" s="14"/>
+      <c r="AV85" s="14"/>
+      <c r="AW85" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="AX85" s="63"/>
+      <c r="AY85" s="63"/>
+      <c r="AZ85" s="63"/>
+      <c r="BA85" s="63"/>
+      <c r="BB85" s="14"/>
+      <c r="BC85" s="14"/>
+      <c r="BD85" s="14"/>
+      <c r="BE85" s="14"/>
+      <c r="BF85" s="14"/>
+      <c r="BG85" s="14"/>
+      <c r="BH85" s="14"/>
+      <c r="BI85" s="14"/>
+      <c r="BJ85" s="14"/>
+      <c r="BK85" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="48">
+    <mergeCell ref="AK72:AL72"/>
+    <mergeCell ref="AN71:AQ71"/>
+    <mergeCell ref="AR74:AV74"/>
+    <mergeCell ref="AZ74:BC74"/>
+    <mergeCell ref="AS51:AW51"/>
+    <mergeCell ref="BA51:BD51"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="D72:H72"/>
+    <mergeCell ref="I73:M73"/>
+    <mergeCell ref="N69:Q69"/>
+    <mergeCell ref="R71:T71"/>
+    <mergeCell ref="U72:Y72"/>
+    <mergeCell ref="Z70:AA70"/>
+    <mergeCell ref="AB73:AF73"/>
+    <mergeCell ref="AG71:AH71"/>
+    <mergeCell ref="AI74:AJ74"/>
+    <mergeCell ref="AP30:AQ30"/>
+    <mergeCell ref="AS30:AW30"/>
+    <mergeCell ref="BA30:BD30"/>
+    <mergeCell ref="B56:B60"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="G46:J46"/>
+    <mergeCell ref="K48:M48"/>
+    <mergeCell ref="O48:P48"/>
+    <mergeCell ref="R48:U48"/>
+    <mergeCell ref="V49:AB49"/>
+    <mergeCell ref="AC50:AL50"/>
+    <mergeCell ref="AM47:AN47"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="Y29:AE29"/>
+    <mergeCell ref="AF28:AO28"/>
+    <mergeCell ref="B35:B39"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G6:R6"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="W5:Y5"/>
     <mergeCell ref="AR8:AU8"/>
     <mergeCell ref="Z4:AA4"/>
     <mergeCell ref="AB8:AC8"/>
     <mergeCell ref="AD5:AE5"/>
     <mergeCell ref="AG8:AK8"/>
     <mergeCell ref="AL5:AO5"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G6:R6"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="W5:Y5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
